--- a/prisma/imports/Sistema clientes dani.xlsx
+++ b/prisma/imports/Sistema clientes dani.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="98">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -95,9 +95,6 @@
     <t xml:space="preserve">nico roa </t>
   </si>
   <si>
-    <t xml:space="preserve">pini hijo </t>
-  </si>
-  <si>
     <t xml:space="preserve">edu morona </t>
   </si>
   <si>
@@ -105,9 +102,6 @@
   </si>
   <si>
     <t xml:space="preserve">home bicicleta </t>
-  </si>
-  <si>
-    <t xml:space="preserve">home claudia </t>
   </si>
   <si>
     <t xml:space="preserve">ariel cajal </t>
@@ -153,9 +147,6 @@
   </si>
   <si>
     <t>nestor molina c/ventil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">luis vecino </t>
   </si>
   <si>
     <t>andy guarepi</t>
@@ -230,9 +221,6 @@
     <t xml:space="preserve">mario romero </t>
   </si>
   <si>
-    <t xml:space="preserve">enzo rodriguez </t>
-  </si>
-  <si>
     <t>gustavo mario</t>
   </si>
   <si>
@@ -260,9 +248,6 @@
     <t xml:space="preserve">laura perez tv 32 </t>
   </si>
   <si>
-    <t xml:space="preserve">kely </t>
-  </si>
-  <si>
     <t xml:space="preserve">godoy daniel </t>
   </si>
   <si>
@@ -287,25 +272,16 @@
     <t xml:space="preserve">jony </t>
   </si>
   <si>
-    <t xml:space="preserve">gustavo ristaino </t>
-  </si>
-  <si>
     <t xml:space="preserve">dario sillas </t>
   </si>
   <si>
     <t xml:space="preserve">javier esteban </t>
   </si>
   <si>
-    <t xml:space="preserve">brenda uñas </t>
-  </si>
-  <si>
     <t xml:space="preserve">mariana peros </t>
   </si>
   <si>
     <t>eliseo sosa tv 32 oul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cuty tender </t>
   </si>
   <si>
     <t xml:space="preserve">cristian </t>
@@ -317,7 +293,43 @@
     <t>diego keberlein</t>
   </si>
   <si>
-    <t>ivan</t>
+    <t xml:space="preserve">mabel ortiz </t>
+  </si>
+  <si>
+    <t>fer herrera parlante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hori </t>
+  </si>
+  <si>
+    <t xml:space="preserve">zotelo cubiertas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">jose ortiz eft </t>
+  </si>
+  <si>
+    <t>mario romero a17 256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">julito 2t </t>
+  </si>
+  <si>
+    <t xml:space="preserve">omar casco tv </t>
+  </si>
+  <si>
+    <t>cristian debe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valeria ramon </t>
+  </si>
+  <si>
+    <t>zotelo bici</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brenda uña </t>
+  </si>
+  <si>
+    <t>marcelo hori motos</t>
   </si>
 </sst>
 </file>
@@ -327,7 +339,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -355,13 +367,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -450,7 +455,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -473,12 +478,11 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -926,7 +930,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -937,7 +941,7 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:M237"/>
+  <dimension ref="A1:M223"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.58203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="18.58203125" customWidth="1"/>
@@ -945,7 +949,7 @@
     <col min="4" max="4" width="4.08203125" customWidth="1"/>
     <col min="5" max="5" width="15.5" customWidth="1"/>
     <col min="6" max="6" width="15.58203125" style="14" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" customWidth="1"/>
+    <col min="7" max="7" width="17.83203125" customWidth="1"/>
     <col min="8" max="8" width="19" style="11" customWidth="1"/>
     <col min="9" max="9" width="13.83203125" customWidth="1"/>
     <col min="10" max="10" width="8.83203125" customWidth="1"/>
@@ -955,7 +959,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
@@ -1012,7 +1016,7 @@
         <v>200000</v>
       </c>
       <c r="F2" s="13">
-        <f t="shared" ref="F2:F14" si="0">G2-H2</f>
+        <f t="shared" ref="F2:F12" si="0">G2-H2</f>
         <v>3900000</v>
       </c>
       <c r="G2" s="7">
@@ -1022,59 +1026,59 @@
         <v>2500000</v>
       </c>
       <c r="I2" s="2">
-        <f t="shared" ref="I2:I14" si="1">IF(F2=0,"",IF(C2="CRED",B2+(INT((G2-F2)/E2)+1)*D2,B2+INT((G2-F2)/E2)*D2))</f>
+        <f t="shared" ref="I2:I12" si="1">IF(F2=0,"",IF(C2="CRED",B2+(INT((G2-F2)/E2)+1)*D2,B2+INT((G2-F2)/E2)*D2))</f>
         <v>46032</v>
       </c>
       <c r="J2" s="1">
-        <f t="shared" ref="J2:J14" ca="1" si="2">IF(I2="","",I2-TODAY())</f>
-        <v>-102</v>
+        <f t="shared" ref="J2:J12" ca="1" si="2">IF(I2="","",I2-TODAY())</f>
+        <v>-116</v>
       </c>
       <c r="K2" s="3" t="str">
-        <f t="shared" ref="K2:K14" ca="1" si="3">IF(J2="","",IF(J2&lt;0,"VENCIDO",IF(J2&lt;=1,"PRÓXIMO","VIGENTE")))</f>
+        <f t="shared" ref="K2:K12" ca="1" si="3">IF(J2="","",IF(J2&lt;0,"VENCIDO",IF(J2&lt;=1,"PRÓXIMO","VIGENTE")))</f>
         <v>VENCIDO</v>
       </c>
       <c r="L2" s="1">
-        <f t="shared" ref="L2:L14" si="4">IF(F2=G2,0,INT((G2-F2)/E2))</f>
+        <f t="shared" ref="L2:L12" si="4">IF(F2=G2,0,INT((G2-F2)/E2))</f>
         <v>12</v>
       </c>
       <c r="M2" s="1">
-        <f t="shared" ref="M2:M14" si="5">IF(F2=0,0,INT(F2/E2)+(IF(MOD(F2,E2)&gt;0,1,0)))</f>
+        <f t="shared" ref="M2:M12" si="5">IF(F2=0,0,INT(F2/E2)+(IF(MOD(F2,E2)&gt;0,1,0)))</f>
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15.75" customHeight="1">
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2">
-        <v>45919</v>
+        <v>45933</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E3" s="7">
-        <v>32000</v>
+        <v>300000</v>
       </c>
       <c r="F3" s="13">
         <f t="shared" si="0"/>
-        <v>74000</v>
+        <v>1500000</v>
       </c>
       <c r="G3" s="7">
-        <v>96000</v>
-      </c>
-      <c r="H3" s="20">
-        <v>22000</v>
+        <v>3900000</v>
+      </c>
+      <c r="H3" s="10">
+        <v>2400000</v>
       </c>
       <c r="I3" s="2">
         <f t="shared" si="1"/>
-        <v>45949</v>
+        <v>46068</v>
       </c>
       <c r="J3" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-185</v>
+        <v>-80</v>
       </c>
       <c r="K3" s="3" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -1082,54 +1086,54 @@
       </c>
       <c r="L3" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M3" s="1">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>35</v>
+      <c r="A4" s="18" t="s">
+        <v>19</v>
       </c>
       <c r="B4" s="2">
-        <v>45933</v>
+        <v>46083</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="1">
-        <v>15</v>
-      </c>
-      <c r="E4" s="7">
-        <v>300000</v>
+        <v>30</v>
+      </c>
+      <c r="E4" s="19">
+        <v>743000</v>
       </c>
       <c r="F4" s="13">
         <f t="shared" si="0"/>
-        <v>1500000</v>
+        <v>3715000</v>
       </c>
       <c r="G4" s="7">
-        <v>3900000</v>
+        <v>5201000</v>
       </c>
       <c r="H4" s="10">
-        <v>2400000</v>
+        <v>1486000</v>
       </c>
       <c r="I4" s="2">
         <f t="shared" si="1"/>
-        <v>46068</v>
+        <v>46173</v>
       </c>
       <c r="J4" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-66</v>
+        <v>25</v>
       </c>
       <c r="K4" s="3" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>VENCIDO</v>
+        <v>VIGENTE</v>
       </c>
       <c r="L4" s="1">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M4" s="1">
         <f t="shared" si="5"/>
@@ -1137,11 +1141,11 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B5" s="2">
-        <v>46083</v>
+        <v>45701</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
@@ -1149,38 +1153,38 @@
       <c r="D5" s="1">
         <v>30</v>
       </c>
-      <c r="E5" s="19">
-        <v>743000</v>
+      <c r="E5" s="7">
+        <v>400000</v>
       </c>
       <c r="F5" s="13">
         <f t="shared" si="0"/>
-        <v>3715000</v>
+        <v>1200000</v>
       </c>
       <c r="G5" s="7">
-        <v>5201000</v>
+        <v>6000000</v>
       </c>
       <c r="H5" s="10">
-        <v>1486000</v>
+        <v>4800000</v>
       </c>
       <c r="I5" s="2">
         <f t="shared" si="1"/>
-        <v>46173</v>
+        <v>46091</v>
       </c>
       <c r="J5" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>39</v>
+        <v>-57</v>
       </c>
       <c r="K5" s="3" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>VIGENTE</v>
+        <v>VENCIDO</v>
       </c>
       <c r="L5" s="1">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M5" s="1">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1188,7 +1192,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="2">
-        <v>45701</v>
+        <v>46087</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>14</v>
@@ -1197,25 +1201,25 @@
         <v>30</v>
       </c>
       <c r="E6" s="7">
-        <v>400000</v>
+        <v>123000</v>
       </c>
       <c r="F6" s="13">
         <f t="shared" si="0"/>
-        <v>1200000</v>
+        <v>492000</v>
       </c>
       <c r="G6" s="7">
-        <v>6000000</v>
+        <v>615000</v>
       </c>
       <c r="H6" s="10">
-        <v>4800000</v>
+        <v>123000</v>
       </c>
       <c r="I6" s="2">
         <f t="shared" si="1"/>
-        <v>46091</v>
+        <v>46147</v>
       </c>
       <c r="J6" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-43</v>
+        <v>-1</v>
       </c>
       <c r="K6" s="3" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -1223,11 +1227,11 @@
       </c>
       <c r="L6" s="1">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M6" s="1">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1235,7 +1239,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="2">
-        <v>46087</v>
+        <v>45860</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>14</v>
@@ -1244,25 +1248,25 @@
         <v>30</v>
       </c>
       <c r="E7" s="7">
-        <v>123000</v>
+        <v>200000</v>
       </c>
       <c r="F7" s="13">
         <f t="shared" si="0"/>
-        <v>492000</v>
+        <v>200000</v>
       </c>
       <c r="G7" s="7">
-        <v>615000</v>
+        <v>2000000</v>
       </c>
       <c r="H7" s="10">
-        <v>123000</v>
+        <v>1800000</v>
       </c>
       <c r="I7" s="2">
         <f t="shared" si="1"/>
-        <v>46147</v>
+        <v>46160</v>
       </c>
       <c r="J7" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K7" s="3" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -1270,19 +1274,19 @@
       </c>
       <c r="L7" s="1">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M7" s="1">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="18" t="s">
         <v>23</v>
       </c>
       <c r="B8" s="2">
-        <v>45714</v>
+        <v>45905</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
@@ -1291,25 +1295,25 @@
         <v>30</v>
       </c>
       <c r="E8" s="7">
-        <v>200000</v>
+        <v>1200000</v>
       </c>
       <c r="F8" s="13">
         <f t="shared" si="0"/>
-        <v>200000</v>
+        <v>7300000</v>
       </c>
       <c r="G8" s="7">
-        <v>2400000</v>
+        <v>14400000</v>
       </c>
       <c r="H8" s="10">
-        <v>2200000</v>
+        <v>7100000</v>
       </c>
       <c r="I8" s="2">
         <f t="shared" si="1"/>
-        <v>46074</v>
+        <v>46085</v>
       </c>
       <c r="J8" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-60</v>
+        <v>-63</v>
       </c>
       <c r="K8" s="3" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -1317,11 +1321,11 @@
       </c>
       <c r="L8" s="1">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M8" s="1">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1329,34 +1333,34 @@
         <v>24</v>
       </c>
       <c r="B9" s="2">
-        <v>45860</v>
+        <v>46018</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="1">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E9" s="7">
-        <v>200000</v>
+        <v>57000</v>
       </c>
       <c r="F9" s="13">
         <f t="shared" si="0"/>
-        <v>400000</v>
+        <v>453000</v>
       </c>
       <c r="G9" s="7">
-        <v>2000000</v>
+        <v>1254000</v>
       </c>
       <c r="H9" s="10">
-        <v>1600000</v>
+        <v>801000</v>
       </c>
       <c r="I9" s="2">
         <f t="shared" si="1"/>
-        <v>46130</v>
+        <v>46123</v>
       </c>
       <c r="J9" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-25</v>
       </c>
       <c r="K9" s="3" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -1364,19 +1368,19 @@
       </c>
       <c r="L9" s="1">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M9" s="1">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="2">
-        <v>45905</v>
+        <v>45906</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>14</v>
@@ -1385,25 +1389,23 @@
         <v>30</v>
       </c>
       <c r="E10" s="7">
-        <v>1200000</v>
+        <v>900000</v>
       </c>
       <c r="F10" s="13">
         <f t="shared" si="0"/>
-        <v>7300000</v>
+        <v>900000</v>
       </c>
       <c r="G10" s="7">
-        <v>14400000</v>
-      </c>
-      <c r="H10" s="10">
-        <v>7100000</v>
-      </c>
+        <v>900000</v>
+      </c>
+      <c r="H10" s="10"/>
       <c r="I10" s="2">
         <f t="shared" si="1"/>
-        <v>46085</v>
+        <v>45936</v>
       </c>
       <c r="J10" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-49</v>
+        <v>-212</v>
       </c>
       <c r="K10" s="3" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -1411,46 +1413,46 @@
       </c>
       <c r="L10" s="1">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M10" s="1">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B11" s="2">
-        <v>46018</v>
+        <v>45931</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D11" s="1">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E11" s="7">
-        <v>57000</v>
+        <v>150000</v>
       </c>
       <c r="F11" s="13">
         <f t="shared" si="0"/>
-        <v>567000</v>
+        <v>287000</v>
       </c>
       <c r="G11" s="7">
-        <v>1254000</v>
+        <v>732000</v>
       </c>
       <c r="H11" s="10">
-        <v>687000</v>
+        <v>445000</v>
       </c>
       <c r="I11" s="2">
         <f t="shared" si="1"/>
-        <v>46109</v>
+        <v>46021</v>
       </c>
       <c r="J11" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-25</v>
+        <v>-127</v>
       </c>
       <c r="K11" s="3" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -1458,44 +1460,46 @@
       </c>
       <c r="L11" s="1">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M11" s="1">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="2">
-        <v>45906</v>
+        <v>45937</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="1">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>900000</v>
+        <v>28000</v>
       </c>
       <c r="F12" s="13">
         <f t="shared" si="0"/>
-        <v>900000</v>
+        <v>26000</v>
       </c>
       <c r="G12" s="7">
-        <v>900000</v>
-      </c>
-      <c r="H12" s="10"/>
+        <v>504000</v>
+      </c>
+      <c r="H12" s="10">
+        <v>478000</v>
+      </c>
       <c r="I12" s="2">
         <f t="shared" si="1"/>
-        <v>45936</v>
+        <v>46063</v>
       </c>
       <c r="J12" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-198</v>
+        <v>-85</v>
       </c>
       <c r="K12" s="3" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -1503,7 +1507,7 @@
       </c>
       <c r="L12" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M12" s="1">
         <f t="shared" si="5"/>
@@ -1512,57 +1516,57 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B13" s="2">
-        <v>45931</v>
+        <v>45916</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="1">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E13" s="7">
-        <v>150000</v>
+        <v>50000</v>
       </c>
       <c r="F13" s="13">
-        <f t="shared" si="0"/>
-        <v>287000</v>
+        <f t="shared" ref="F13:F31" si="6">G13-H13</f>
+        <v>823000</v>
       </c>
       <c r="G13" s="7">
-        <v>732000</v>
+        <v>1280000</v>
       </c>
       <c r="H13" s="10">
-        <v>445000</v>
+        <v>457000</v>
       </c>
       <c r="I13" s="2">
-        <f t="shared" si="1"/>
-        <v>46021</v>
+        <f t="shared" ref="I13:I31" si="7">IF(F13=0,"",IF(C13="CRED",B13+(INT((G13-F13)/E13)+1)*D13,B13+INT((G13-F13)/E13)*D13))</f>
+        <v>45986</v>
       </c>
       <c r="J13" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-113</v>
+        <f t="shared" ref="J13:J31" ca="1" si="8">IF(I13="","",I13-TODAY())</f>
+        <v>-162</v>
       </c>
       <c r="K13" s="3" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ref="K13:K31" ca="1" si="9">IF(J13="","",IF(J13&lt;0,"VENCIDO",IF(J13&lt;=1,"PRÓXIMO","VIGENTE")))</f>
         <v>VENCIDO</v>
       </c>
       <c r="L13" s="1">
-        <f t="shared" si="4"/>
-        <v>2</v>
+        <f t="shared" ref="L13:L31" si="10">IF(F13=G13,0,INT((G13-F13)/E13))</f>
+        <v>9</v>
       </c>
       <c r="M13" s="1">
-        <f t="shared" si="5"/>
-        <v>2</v>
+        <f t="shared" ref="M13:M31" si="11">IF(F13=0,0,INT(F13/E13)+(IF(MOD(F13,E13)&gt;0,1,0)))</f>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B14" s="2">
-        <v>45937</v>
+        <v>46102</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>14</v>
@@ -1571,37 +1575,37 @@
         <v>7</v>
       </c>
       <c r="E14" s="7">
-        <v>28000</v>
+        <v>150000</v>
       </c>
       <c r="F14" s="13">
-        <f t="shared" si="0"/>
-        <v>26000</v>
+        <f t="shared" si="6"/>
+        <v>4550000</v>
       </c>
       <c r="G14" s="7">
-        <v>504000</v>
+        <v>5250000</v>
       </c>
       <c r="H14" s="10">
-        <v>478000</v>
+        <v>700000</v>
       </c>
       <c r="I14" s="2">
-        <f t="shared" si="1"/>
-        <v>46063</v>
+        <f t="shared" si="7"/>
+        <v>46137</v>
       </c>
       <c r="J14" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-71</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>-11</v>
       </c>
       <c r="K14" s="3" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="9"/>
         <v>VENCIDO</v>
       </c>
       <c r="L14" s="1">
-        <f t="shared" si="4"/>
-        <v>17</v>
+        <f t="shared" si="10"/>
+        <v>4</v>
       </c>
       <c r="M14" s="1">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1609,171 +1613,171 @@
         <v>29</v>
       </c>
       <c r="B15" s="2">
-        <v>45916</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>45957</v>
+      </c>
+      <c r="C15" s="1"/>
       <c r="D15" s="1">
         <v>7</v>
       </c>
       <c r="E15" s="7">
-        <v>50000</v>
+        <v>27000</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" ref="F15:F34" si="6">G15-H15</f>
-        <v>823000</v>
+        <f t="shared" si="6"/>
+        <v>240000</v>
       </c>
       <c r="G15" s="7">
-        <v>1280000</v>
+        <v>432000</v>
       </c>
       <c r="H15" s="10">
-        <v>457000</v>
+        <v>192000</v>
       </c>
       <c r="I15" s="2">
-        <f t="shared" ref="I15:I34" si="7">IF(F15=0,"",IF(C15="CRED",B15+(INT((G15-F15)/E15)+1)*D15,B15+INT((G15-F15)/E15)*D15))</f>
-        <v>45986</v>
+        <f t="shared" si="7"/>
+        <v>46006</v>
       </c>
       <c r="J15" s="1">
-        <f t="shared" ref="J15:J34" ca="1" si="8">IF(I15="","",I15-TODAY())</f>
-        <v>-148</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>-142</v>
       </c>
       <c r="K15" s="3" t="str">
-        <f t="shared" ref="K15:K34" ca="1" si="9">IF(J15="","",IF(J15&lt;0,"VENCIDO",IF(J15&lt;=1,"PRÓXIMO","VIGENTE")))</f>
+        <f t="shared" ca="1" si="9"/>
         <v>VENCIDO</v>
       </c>
       <c r="L15" s="1">
-        <f t="shared" ref="L15:L34" si="10">IF(F15=G15,0,INT((G15-F15)/E15))</f>
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="M15" s="1">
+        <f t="shared" si="11"/>
         <v>9</v>
-      </c>
-      <c r="M15" s="1">
-        <f t="shared" ref="M15:M34" si="11">IF(F15=0,0,INT(F15/E15)+(IF(MOD(F15,E15)&gt;0,1,0)))</f>
-        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="B16" s="2">
-        <v>46102</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>46081</v>
+      </c>
+      <c r="C16" s="1"/>
       <c r="D16" s="1">
         <v>7</v>
       </c>
       <c r="E16" s="7">
-        <v>150000</v>
+        <v>1</v>
       </c>
       <c r="F16" s="13">
         <f t="shared" si="6"/>
-        <v>4800000</v>
+        <v>938000</v>
       </c>
       <c r="G16" s="7">
-        <v>5250000</v>
+        <v>1088000</v>
       </c>
       <c r="H16" s="10">
-        <v>450000</v>
+        <v>150000</v>
       </c>
       <c r="I16" s="2">
         <f t="shared" si="7"/>
-        <v>46130</v>
+        <v>1096081</v>
       </c>
       <c r="J16" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>-4</v>
+        <v>1049933</v>
       </c>
       <c r="K16" s="3" t="str">
         <f t="shared" ca="1" si="9"/>
-        <v>VENCIDO</v>
+        <v>VIGENTE</v>
       </c>
       <c r="L16" s="1">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>150000</v>
       </c>
       <c r="M16" s="1">
         <f t="shared" si="11"/>
-        <v>32</v>
+        <v>938000</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B17" s="2">
-        <v>45957</v>
-      </c>
-      <c r="C17" s="1"/>
+        <v>46009</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="D17" s="1">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E17" s="7">
-        <v>27000</v>
+        <v>235000</v>
       </c>
       <c r="F17" s="13">
         <f t="shared" si="6"/>
-        <v>240000</v>
+        <v>470000</v>
       </c>
       <c r="G17" s="7">
-        <v>432000</v>
+        <v>1410000</v>
       </c>
       <c r="H17" s="10">
-        <v>192000</v>
+        <v>940000</v>
       </c>
       <c r="I17" s="2">
         <f t="shared" si="7"/>
-        <v>46006</v>
+        <v>46159</v>
       </c>
       <c r="J17" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>-128</v>
+        <v>11</v>
       </c>
       <c r="K17" s="3" t="str">
         <f t="shared" ca="1" si="9"/>
-        <v>VENCIDO</v>
+        <v>VIGENTE</v>
       </c>
       <c r="L17" s="1">
         <f t="shared" si="10"/>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M17" s="1">
         <f t="shared" si="11"/>
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="2">
+        <v>45980</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="1">
         <v>30</v>
       </c>
-      <c r="B18" s="2">
-        <v>46081</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1">
-        <v>7</v>
-      </c>
       <c r="E18" s="7">
-        <v>1</v>
+        <v>63000</v>
       </c>
       <c r="F18" s="13">
         <f t="shared" si="6"/>
-        <v>938000</v>
+        <v>126000</v>
       </c>
       <c r="G18" s="7">
-        <v>1088000</v>
+        <v>441000</v>
       </c>
       <c r="H18" s="10">
-        <v>150000</v>
+        <v>315000</v>
       </c>
       <c r="I18" s="2">
         <f t="shared" si="7"/>
-        <v>1096081</v>
+        <v>46160</v>
       </c>
       <c r="J18" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>1049947</v>
+        <v>12</v>
       </c>
       <c r="K18" s="3" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -1781,19 +1785,19 @@
       </c>
       <c r="L18" s="1">
         <f t="shared" si="10"/>
-        <v>150000</v>
+        <v>5</v>
       </c>
       <c r="M18" s="1">
         <f t="shared" si="11"/>
-        <v>938000</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B19" s="2">
-        <v>46009</v>
+        <v>46063</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>14</v>
@@ -1802,25 +1806,25 @@
         <v>30</v>
       </c>
       <c r="E19" s="7">
-        <v>235000</v>
+        <v>163000</v>
       </c>
       <c r="F19" s="13">
         <f t="shared" si="6"/>
-        <v>470000</v>
+        <v>489000</v>
       </c>
       <c r="G19" s="7">
-        <v>1410000</v>
+        <v>815000</v>
       </c>
       <c r="H19" s="10">
-        <v>940000</v>
+        <v>326000</v>
       </c>
       <c r="I19" s="2">
         <f t="shared" si="7"/>
-        <v>46159</v>
+        <v>46153</v>
       </c>
       <c r="J19" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="K19" s="3" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -1828,19 +1832,19 @@
       </c>
       <c r="L19" s="1">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M19" s="1">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B20" s="2">
-        <v>45978</v>
+        <v>45997</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>14</v>
@@ -1849,23 +1853,25 @@
         <v>30</v>
       </c>
       <c r="E20" s="7">
-        <v>84000</v>
+        <v>160000</v>
       </c>
       <c r="F20" s="13">
         <f t="shared" si="6"/>
-        <v>84000</v>
+        <v>160000</v>
       </c>
       <c r="G20" s="7">
-        <v>84000</v>
-      </c>
-      <c r="H20" s="10"/>
+        <v>800000</v>
+      </c>
+      <c r="H20" s="10">
+        <v>640000</v>
+      </c>
       <c r="I20" s="2">
         <f t="shared" si="7"/>
-        <v>46008</v>
+        <v>46147</v>
       </c>
       <c r="J20" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>-126</v>
+        <v>-1</v>
       </c>
       <c r="K20" s="3" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -1873,7 +1879,7 @@
       </c>
       <c r="L20" s="1">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M20" s="1">
         <f t="shared" si="11"/>
@@ -1881,11 +1887,11 @@
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="18" t="s">
-        <v>40</v>
+      <c r="A21" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="B21" s="2">
-        <v>45980</v>
+        <v>46067</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>14</v>
@@ -1894,25 +1900,25 @@
         <v>30</v>
       </c>
       <c r="E21" s="7">
-        <v>63000</v>
+        <v>208000</v>
       </c>
       <c r="F21" s="13">
         <f t="shared" si="6"/>
-        <v>126000</v>
+        <v>1720000</v>
       </c>
       <c r="G21" s="7">
-        <v>441000</v>
+        <v>3421000</v>
       </c>
       <c r="H21" s="10">
-        <v>315000</v>
+        <v>1701000</v>
       </c>
       <c r="I21" s="2">
         <f t="shared" si="7"/>
-        <v>46160</v>
+        <v>46337</v>
       </c>
       <c r="J21" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K21" s="3" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -1920,11 +1926,11 @@
       </c>
       <c r="L21" s="1">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M21" s="1">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1932,7 +1938,7 @@
         <v>44</v>
       </c>
       <c r="B22" s="2">
-        <v>46063</v>
+        <v>46001</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>14</v>
@@ -1941,37 +1947,37 @@
         <v>30</v>
       </c>
       <c r="E22" s="7">
-        <v>163000</v>
+        <v>217000</v>
       </c>
       <c r="F22" s="13">
         <f t="shared" si="6"/>
-        <v>652000</v>
+        <v>1736000</v>
       </c>
       <c r="G22" s="7">
-        <v>815000</v>
+        <v>2604000</v>
       </c>
       <c r="H22" s="10">
-        <v>163000</v>
+        <v>868000</v>
       </c>
       <c r="I22" s="2">
         <f t="shared" si="7"/>
-        <v>46123</v>
+        <v>46151</v>
       </c>
       <c r="J22" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>-11</v>
+        <v>3</v>
       </c>
       <c r="K22" s="3" t="str">
         <f t="shared" ca="1" si="9"/>
-        <v>VENCIDO</v>
+        <v>VIGENTE</v>
       </c>
       <c r="L22" s="1">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M22" s="1">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1979,7 +1985,7 @@
         <v>45</v>
       </c>
       <c r="B23" s="2">
-        <v>45997</v>
+        <v>46008</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>14</v>
@@ -1988,25 +1994,25 @@
         <v>30</v>
       </c>
       <c r="E23" s="7">
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="F23" s="13">
         <f t="shared" si="6"/>
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="G23" s="7">
+        <v>1000000</v>
+      </c>
+      <c r="H23" s="10">
         <v>800000</v>
-      </c>
-      <c r="H23" s="10">
-        <v>640000</v>
       </c>
       <c r="I23" s="2">
         <f t="shared" si="7"/>
-        <v>46147</v>
+        <v>46158</v>
       </c>
       <c r="J23" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K23" s="3" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -2026,7 +2032,7 @@
         <v>46</v>
       </c>
       <c r="B24" s="2">
-        <v>46067</v>
+        <v>46105</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>14</v>
@@ -2035,25 +2041,25 @@
         <v>30</v>
       </c>
       <c r="E24" s="7">
-        <v>208000</v>
+        <v>291000</v>
       </c>
       <c r="F24" s="13">
         <f t="shared" si="6"/>
-        <v>820000</v>
+        <v>873000</v>
       </c>
       <c r="G24" s="7">
-        <v>2521000</v>
+        <v>1164000</v>
       </c>
       <c r="H24" s="10">
-        <v>1701000</v>
+        <v>291000</v>
       </c>
       <c r="I24" s="2">
         <f t="shared" si="7"/>
-        <v>46337</v>
+        <v>46165</v>
       </c>
       <c r="J24" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>203</v>
+        <v>17</v>
       </c>
       <c r="K24" s="3" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -2061,11 +2067,11 @@
       </c>
       <c r="L24" s="1">
         <f t="shared" si="10"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M24" s="1">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -2073,26 +2079,26 @@
         <v>47</v>
       </c>
       <c r="B25" s="2">
-        <v>46001</v>
+        <v>46030</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D25" s="1">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>217000</v>
+        <v>51000</v>
       </c>
       <c r="F25" s="13">
         <f t="shared" si="6"/>
-        <v>1953000</v>
+        <v>143000</v>
       </c>
       <c r="G25" s="7">
-        <v>2604000</v>
+        <v>765000</v>
       </c>
       <c r="H25" s="10">
-        <v>651000</v>
+        <v>622000</v>
       </c>
       <c r="I25" s="2">
         <f t="shared" si="7"/>
@@ -2100,7 +2106,7 @@
       </c>
       <c r="J25" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>-13</v>
+        <v>-27</v>
       </c>
       <c r="K25" s="3" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -2108,11 +2114,11 @@
       </c>
       <c r="L25" s="1">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="M25" s="1">
         <f t="shared" si="11"/>
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -2120,7 +2126,7 @@
         <v>48</v>
       </c>
       <c r="B26" s="2">
-        <v>46008</v>
+        <v>46011</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>14</v>
@@ -2129,25 +2135,25 @@
         <v>30</v>
       </c>
       <c r="E26" s="7">
-        <v>200000</v>
+        <v>137000</v>
       </c>
       <c r="F26" s="13">
         <f t="shared" si="6"/>
-        <v>200000</v>
+        <v>137000</v>
       </c>
       <c r="G26" s="7">
-        <v>1000000</v>
+        <v>685000</v>
       </c>
       <c r="H26" s="10">
-        <v>800000</v>
+        <v>548000</v>
       </c>
       <c r="I26" s="2">
         <f t="shared" si="7"/>
-        <v>46158</v>
+        <v>46161</v>
       </c>
       <c r="J26" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K26" s="3" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -2167,42 +2173,42 @@
         <v>49</v>
       </c>
       <c r="B27" s="2">
-        <v>46105</v>
+        <v>46015</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D27" s="1">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E27" s="7">
-        <v>291000</v>
+        <v>40000</v>
       </c>
       <c r="F27" s="13">
         <f t="shared" si="6"/>
-        <v>873000</v>
+        <v>120000</v>
       </c>
       <c r="G27" s="7">
-        <v>1164000</v>
+        <v>720000</v>
       </c>
       <c r="H27" s="10">
-        <v>291000</v>
+        <v>600000</v>
       </c>
       <c r="I27" s="2">
         <f t="shared" si="7"/>
-        <v>46165</v>
+        <v>46127</v>
       </c>
       <c r="J27" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>31</v>
+        <v>-21</v>
       </c>
       <c r="K27" s="3" t="str">
         <f t="shared" ca="1" si="9"/>
-        <v>VIGENTE</v>
+        <v>VENCIDO</v>
       </c>
       <c r="L27" s="1">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M27" s="1">
         <f t="shared" si="11"/>
@@ -2214,101 +2220,101 @@
         <v>50</v>
       </c>
       <c r="B28" s="2">
-        <v>46030</v>
+        <v>46015</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D28" s="1">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E28" s="7">
-        <v>51000</v>
+        <v>110000</v>
       </c>
       <c r="F28" s="13">
         <f t="shared" si="6"/>
-        <v>143000</v>
+        <v>660000</v>
       </c>
       <c r="G28" s="7">
-        <v>765000</v>
+        <v>1100000</v>
       </c>
       <c r="H28" s="10">
-        <v>622000</v>
+        <v>440000</v>
       </c>
       <c r="I28" s="2">
         <f t="shared" si="7"/>
-        <v>46121</v>
+        <v>46165</v>
       </c>
       <c r="J28" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>-13</v>
+        <v>17</v>
       </c>
       <c r="K28" s="3" t="str">
         <f t="shared" ca="1" si="9"/>
-        <v>VENCIDO</v>
+        <v>VIGENTE</v>
       </c>
       <c r="L28" s="1">
         <f t="shared" si="10"/>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M28" s="1">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="1" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="B29" s="2">
-        <v>46011</v>
+        <v>45932</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D29" s="1">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E29" s="7">
-        <v>137000</v>
+        <v>60000</v>
       </c>
       <c r="F29" s="13">
         <f t="shared" si="6"/>
-        <v>137000</v>
+        <v>781000</v>
       </c>
       <c r="G29" s="7">
-        <v>685000</v>
+        <v>1800000</v>
       </c>
       <c r="H29" s="10">
-        <v>548000</v>
+        <v>1019000</v>
       </c>
       <c r="I29" s="2">
         <f t="shared" si="7"/>
-        <v>46161</v>
+        <v>46051</v>
       </c>
       <c r="J29" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>27</v>
+        <v>-97</v>
       </c>
       <c r="K29" s="3" t="str">
         <f t="shared" ca="1" si="9"/>
-        <v>VIGENTE</v>
+        <v>VENCIDO</v>
       </c>
       <c r="L29" s="1">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="M29" s="1">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="B30" s="2">
-        <v>46015</v>
+        <v>46022</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>14</v>
@@ -2317,25 +2323,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>40000</v>
+        <v>560000</v>
       </c>
       <c r="F30" s="13">
         <f t="shared" si="6"/>
-        <v>120000</v>
+        <v>3540000</v>
       </c>
       <c r="G30" s="7">
-        <v>720000</v>
+        <v>5600000</v>
       </c>
       <c r="H30" s="10">
-        <v>600000</v>
+        <v>2060000</v>
       </c>
       <c r="I30" s="2">
         <f t="shared" si="7"/>
-        <v>46127</v>
+        <v>46050</v>
       </c>
       <c r="J30" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>-7</v>
+        <v>-98</v>
       </c>
       <c r="K30" s="3" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -2343,279 +2349,277 @@
       </c>
       <c r="L30" s="1">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="M30" s="1">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B31" s="2">
-        <v>46015</v>
+        <v>45920</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D31" s="1">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>110000</v>
+        <v>37000</v>
       </c>
       <c r="F31" s="13">
         <f t="shared" si="6"/>
-        <v>770000</v>
+        <v>115000</v>
       </c>
       <c r="G31" s="7">
-        <v>1100000</v>
+        <v>832000</v>
       </c>
       <c r="H31" s="10">
-        <v>330000</v>
+        <v>717000</v>
       </c>
       <c r="I31" s="2">
         <f t="shared" si="7"/>
-        <v>46135</v>
+        <v>46060</v>
       </c>
       <c r="J31" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>1</v>
+        <v>-88</v>
       </c>
       <c r="K31" s="3" t="str">
         <f t="shared" ca="1" si="9"/>
-        <v>PRÓXIMO</v>
+        <v>VENCIDO</v>
       </c>
       <c r="L31" s="1">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="M31" s="1">
         <f t="shared" si="11"/>
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="1" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="B32" s="2">
-        <v>45932</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>46030</v>
+      </c>
+      <c r="C32" s="1"/>
       <c r="D32" s="1">
         <v>7</v>
       </c>
       <c r="E32" s="7">
-        <v>60000</v>
+        <v>106000</v>
       </c>
       <c r="F32" s="13">
-        <f t="shared" si="6"/>
-        <v>781000</v>
+        <f t="shared" ref="F32:F68" si="12">G32-H32</f>
+        <v>1284000</v>
       </c>
       <c r="G32" s="7">
-        <v>1800000</v>
+        <v>2120000</v>
       </c>
       <c r="H32" s="10">
-        <v>1019000</v>
+        <v>836000</v>
       </c>
       <c r="I32" s="2">
-        <f t="shared" si="7"/>
-        <v>46051</v>
+        <f t="shared" ref="I32:I68" si="13">IF(F32=0,"",IF(C32="CRED",B32+(INT((G32-F32)/E32)+1)*D32,B32+INT((G32-F32)/E32)*D32))</f>
+        <v>46079</v>
       </c>
       <c r="J32" s="1">
-        <f t="shared" ca="1" si="8"/>
-        <v>-83</v>
+        <f t="shared" ref="J32:J68" ca="1" si="14">IF(I32="","",I32-TODAY())</f>
+        <v>-69</v>
       </c>
       <c r="K32" s="3" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ref="K32:K68" ca="1" si="15">IF(J32="","",IF(J32&lt;0,"VENCIDO",IF(J32&lt;=1,"PRÓXIMO","VIGENTE")))</f>
         <v>VENCIDO</v>
       </c>
       <c r="L32" s="1">
-        <f t="shared" si="10"/>
-        <v>16</v>
+        <f t="shared" ref="L32:L68" si="16">IF(F32=G32,0,INT((G32-F32)/E32))</f>
+        <v>7</v>
       </c>
       <c r="M32" s="1">
-        <f t="shared" si="11"/>
-        <v>14</v>
+        <f t="shared" ref="M32:M68" si="17">IF(F32=0,0,INT(F32/E32)+(IF(MOD(F32,E32)&gt;0,1,0)))</f>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="1" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="B33" s="2">
-        <v>46022</v>
+        <v>46036</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="D33" s="1">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E33" s="7">
-        <v>560000</v>
+        <v>250000</v>
       </c>
       <c r="F33" s="13">
-        <f t="shared" si="6"/>
-        <v>4040000</v>
+        <f t="shared" si="12"/>
+        <v>150000</v>
       </c>
       <c r="G33" s="7">
-        <v>5600000</v>
+        <v>250000</v>
       </c>
       <c r="H33" s="10">
-        <v>1560000</v>
+        <v>100000</v>
       </c>
       <c r="I33" s="2">
-        <f t="shared" si="7"/>
-        <v>46043</v>
+        <f t="shared" si="13"/>
+        <v>46036</v>
       </c>
       <c r="J33" s="1">
-        <f t="shared" ca="1" si="8"/>
-        <v>-91</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-112</v>
       </c>
       <c r="K33" s="3" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="15"/>
         <v>VENCIDO</v>
       </c>
       <c r="L33" s="1">
-        <f t="shared" si="10"/>
-        <v>2</v>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="M33" s="1">
-        <f t="shared" si="11"/>
-        <v>8</v>
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B34" s="2">
-        <v>45920</v>
+        <v>46070</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D34" s="1">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E34" s="7">
-        <v>37000</v>
+        <v>150000</v>
       </c>
       <c r="F34" s="13">
-        <f t="shared" si="6"/>
-        <v>170000</v>
+        <f t="shared" si="12"/>
+        <v>900000</v>
       </c>
       <c r="G34" s="7">
-        <v>832000</v>
+        <v>1200000</v>
       </c>
       <c r="H34" s="10">
-        <v>662000</v>
+        <v>300000</v>
       </c>
       <c r="I34" s="2">
-        <f t="shared" si="7"/>
-        <v>46046</v>
+        <f t="shared" si="13"/>
+        <v>46160</v>
       </c>
       <c r="J34" s="1">
-        <f t="shared" ca="1" si="8"/>
-        <v>-88</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>12</v>
       </c>
       <c r="K34" s="3" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v>VENCIDO</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>VIGENTE</v>
       </c>
       <c r="L34" s="1">
-        <f t="shared" si="10"/>
-        <v>17</v>
+        <f t="shared" si="16"/>
+        <v>2</v>
       </c>
       <c r="M34" s="1">
-        <f t="shared" si="11"/>
-        <v>5</v>
+        <f t="shared" si="17"/>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B35" s="2">
-        <v>46030</v>
-      </c>
-      <c r="C35" s="1"/>
+        <v>46068</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="D35" s="1">
         <v>7</v>
       </c>
       <c r="E35" s="7">
-        <v>106000</v>
+        <v>28000</v>
       </c>
       <c r="F35" s="13">
-        <f t="shared" ref="F35:F80" si="12">G35-H35</f>
-        <v>1390000</v>
+        <f t="shared" si="12"/>
+        <v>224000</v>
       </c>
       <c r="G35" s="7">
-        <v>2120000</v>
+        <v>448000</v>
       </c>
       <c r="H35" s="10">
-        <v>730000</v>
+        <v>224000</v>
       </c>
       <c r="I35" s="2">
-        <f t="shared" ref="I35:I80" si="13">IF(F35=0,"",IF(C35="CRED",B35+(INT((G35-F35)/E35)+1)*D35,B35+INT((G35-F35)/E35)*D35))</f>
-        <v>46072</v>
+        <f t="shared" si="13"/>
+        <v>46131</v>
       </c>
       <c r="J35" s="1">
-        <f t="shared" ref="J35:J80" ca="1" si="14">IF(I35="","",I35-TODAY())</f>
-        <v>-62</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-17</v>
       </c>
       <c r="K35" s="3" t="str">
-        <f t="shared" ref="K35:K80" ca="1" si="15">IF(J35="","",IF(J35&lt;0,"VENCIDO",IF(J35&lt;=1,"PRÓXIMO","VIGENTE")))</f>
+        <f t="shared" ca="1" si="15"/>
         <v>VENCIDO</v>
       </c>
       <c r="L35" s="1">
-        <f t="shared" ref="L35:L80" si="16">IF(F35=G35,0,INT((G35-F35)/E35))</f>
-        <v>6</v>
+        <f t="shared" si="16"/>
+        <v>8</v>
       </c>
       <c r="M35" s="1">
-        <f t="shared" ref="M35:M80" si="17">IF(F35=0,0,INT(F35/E35)+(IF(MOD(F35,E35)&gt;0,1,0)))</f>
-        <v>14</v>
+        <f t="shared" si="17"/>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B36" s="2">
-        <v>46036</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>57</v>
-      </c>
+        <v>46049</v>
+      </c>
+      <c r="C36" s="1"/>
       <c r="D36" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E36" s="7">
-        <v>250000</v>
+        <v>166000</v>
       </c>
       <c r="F36" s="13">
         <f t="shared" si="12"/>
-        <v>150000</v>
+        <v>498000</v>
       </c>
       <c r="G36" s="7">
-        <v>250000</v>
+        <v>996000</v>
       </c>
       <c r="H36" s="10">
-        <v>100000</v>
+        <v>498000</v>
       </c>
       <c r="I36" s="2">
         <f t="shared" si="13"/>
-        <v>46036</v>
+        <v>46139</v>
       </c>
       <c r="J36" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>-98</v>
+        <v>-9</v>
       </c>
       <c r="K36" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -2623,11 +2627,11 @@
       </c>
       <c r="L36" s="1">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M36" s="1">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -2635,34 +2639,32 @@
         <v>58</v>
       </c>
       <c r="B37" s="2">
-        <v>46070</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>46053</v>
+      </c>
+      <c r="C37" s="1"/>
       <c r="D37" s="1">
         <v>30</v>
       </c>
       <c r="E37" s="7">
-        <v>150000</v>
+        <v>90000</v>
       </c>
       <c r="F37" s="13">
         <f t="shared" si="12"/>
-        <v>900000</v>
+        <v>180000</v>
       </c>
       <c r="G37" s="7">
-        <v>1200000</v>
+        <v>540000</v>
       </c>
       <c r="H37" s="10">
-        <v>300000</v>
+        <v>360000</v>
       </c>
       <c r="I37" s="2">
         <f t="shared" si="13"/>
-        <v>46160</v>
+        <v>46173</v>
       </c>
       <c r="J37" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K37" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -2670,58 +2672,58 @@
       </c>
       <c r="L37" s="1">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M37" s="1">
         <f t="shared" si="17"/>
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:13">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="24" t="s">
         <v>59</v>
       </c>
       <c r="B38" s="2">
-        <v>46068</v>
+        <v>46073</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D38" s="1">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E38" s="7">
-        <v>28000</v>
+        <v>400000</v>
       </c>
       <c r="F38" s="13">
         <f t="shared" si="12"/>
-        <v>252000</v>
+        <v>3200000</v>
       </c>
       <c r="G38" s="7">
-        <v>448000</v>
+        <v>4000000</v>
       </c>
       <c r="H38" s="10">
-        <v>196000</v>
+        <v>800000</v>
       </c>
       <c r="I38" s="2">
         <f t="shared" si="13"/>
-        <v>46124</v>
+        <v>46163</v>
       </c>
       <c r="J38" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="K38" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
-        <v>VENCIDO</v>
+        <v>VIGENTE</v>
       </c>
       <c r="L38" s="1">
         <f t="shared" si="16"/>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M38" s="1">
         <f t="shared" si="17"/>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -2729,40 +2731,40 @@
         <v>60</v>
       </c>
       <c r="B39" s="2">
-        <v>46049</v>
+        <v>46057</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
         <v>30</v>
       </c>
       <c r="E39" s="7">
-        <v>166000</v>
+        <v>260000</v>
       </c>
       <c r="F39" s="13">
         <f t="shared" si="12"/>
-        <v>664000</v>
+        <v>1040000</v>
       </c>
       <c r="G39" s="7">
-        <v>996000</v>
+        <v>2080000</v>
       </c>
       <c r="H39" s="10">
-        <v>332000</v>
+        <v>1040000</v>
       </c>
       <c r="I39" s="2">
         <f t="shared" si="13"/>
-        <v>46109</v>
+        <v>46177</v>
       </c>
       <c r="J39" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>-25</v>
+        <v>29</v>
       </c>
       <c r="K39" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
-        <v>VENCIDO</v>
+        <v>VIGENTE</v>
       </c>
       <c r="L39" s="1">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M39" s="1">
         <f t="shared" si="17"/>
@@ -2774,40 +2776,40 @@
         <v>61</v>
       </c>
       <c r="B40" s="2">
-        <v>46053</v>
+        <v>46048</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E40" s="7">
-        <v>90000</v>
+        <v>28000</v>
       </c>
       <c r="F40" s="13">
         <f t="shared" si="12"/>
-        <v>270000</v>
+        <v>76000</v>
       </c>
       <c r="G40" s="7">
-        <v>540000</v>
+        <v>392000</v>
       </c>
       <c r="H40" s="10">
-        <v>270000</v>
+        <v>316000</v>
       </c>
       <c r="I40" s="2">
         <f t="shared" si="13"/>
-        <v>46143</v>
+        <v>46125</v>
       </c>
       <c r="J40" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>9</v>
+        <v>-23</v>
       </c>
       <c r="K40" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
-        <v>VIGENTE</v>
+        <v>VENCIDO</v>
       </c>
       <c r="L40" s="1">
         <f t="shared" si="16"/>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M40" s="1">
         <f t="shared" si="17"/>
@@ -2815,11 +2817,11 @@
       </c>
     </row>
     <row r="41" spans="1:13">
-      <c r="A41" s="25" t="s">
+      <c r="A41" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B41" s="2">
-        <v>46073</v>
+        <v>46066</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>14</v>
@@ -2828,37 +2830,37 @@
         <v>30</v>
       </c>
       <c r="E41" s="7">
-        <v>400000</v>
+        <v>100400</v>
       </c>
       <c r="F41" s="13">
         <f t="shared" si="12"/>
-        <v>3600000</v>
+        <v>303200</v>
       </c>
       <c r="G41" s="7">
-        <v>4000000</v>
+        <v>504000</v>
       </c>
       <c r="H41" s="10">
-        <v>400000</v>
+        <v>200800</v>
       </c>
       <c r="I41" s="2">
         <f t="shared" si="13"/>
-        <v>46133</v>
+        <v>46156</v>
       </c>
       <c r="J41" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K41" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
-        <v>VENCIDO</v>
+        <v>VIGENTE</v>
       </c>
       <c r="L41" s="1">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M41" s="1">
         <f t="shared" si="17"/>
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -2866,32 +2868,34 @@
         <v>63</v>
       </c>
       <c r="B42" s="2">
-        <v>46057</v>
-      </c>
-      <c r="C42" s="1"/>
+        <v>46066</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="D42" s="1">
         <v>30</v>
       </c>
       <c r="E42" s="7">
-        <v>260000</v>
+        <v>169000</v>
       </c>
       <c r="F42" s="13">
         <f t="shared" si="12"/>
-        <v>1300000</v>
+        <v>845000</v>
       </c>
       <c r="G42" s="7">
-        <v>2080000</v>
+        <v>1183000</v>
       </c>
       <c r="H42" s="10">
-        <v>780000</v>
+        <v>338000</v>
       </c>
       <c r="I42" s="2">
         <f t="shared" si="13"/>
-        <v>46147</v>
+        <v>46156</v>
       </c>
       <c r="J42" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K42" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -2899,7 +2903,7 @@
       </c>
       <c r="L42" s="1">
         <f t="shared" si="16"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M42" s="1">
         <f t="shared" si="17"/>
@@ -2911,44 +2915,44 @@
         <v>64</v>
       </c>
       <c r="B43" s="2">
-        <v>46048</v>
+        <v>46067</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1">
         <v>7</v>
       </c>
       <c r="E43" s="7">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="F43" s="13">
         <f t="shared" si="12"/>
-        <v>90000</v>
+        <v>100000</v>
       </c>
       <c r="G43" s="7">
-        <v>390000</v>
+        <v>400000</v>
       </c>
       <c r="H43" s="10">
         <v>300000</v>
       </c>
       <c r="I43" s="2">
         <f t="shared" si="13"/>
-        <v>46118</v>
+        <v>46151</v>
       </c>
       <c r="J43" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>-16</v>
+        <v>3</v>
       </c>
       <c r="K43" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
-        <v>VENCIDO</v>
+        <v>VIGENTE</v>
       </c>
       <c r="L43" s="1">
         <f t="shared" si="16"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M43" s="1">
         <f t="shared" si="17"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -2956,32 +2960,34 @@
         <v>65</v>
       </c>
       <c r="B44" s="2">
-        <v>46048</v>
-      </c>
-      <c r="C44" s="1"/>
+        <v>46073</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="D44" s="1">
         <v>7</v>
       </c>
       <c r="E44" s="7">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="F44" s="13">
         <f t="shared" si="12"/>
-        <v>76000</v>
+        <v>600000</v>
       </c>
       <c r="G44" s="7">
-        <v>392000</v>
+        <v>750000</v>
       </c>
       <c r="H44" s="10">
-        <v>316000</v>
+        <v>150000</v>
       </c>
       <c r="I44" s="2">
         <f t="shared" si="13"/>
-        <v>46125</v>
+        <v>46115</v>
       </c>
       <c r="J44" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>-9</v>
+        <v>-33</v>
       </c>
       <c r="K44" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -2989,11 +2995,11 @@
       </c>
       <c r="L44" s="1">
         <f t="shared" si="16"/>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M44" s="1">
         <f t="shared" si="17"/>
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -3001,34 +3007,34 @@
         <v>66</v>
       </c>
       <c r="B45" s="2">
-        <v>46066</v>
+        <v>46078</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="D45" s="1">
         <v>30</v>
       </c>
       <c r="E45" s="7">
-        <v>100400</v>
+        <v>150000</v>
       </c>
       <c r="F45" s="13">
         <f t="shared" si="12"/>
-        <v>303200</v>
+        <v>1050000</v>
       </c>
       <c r="G45" s="7">
-        <v>504000</v>
+        <v>1500000</v>
       </c>
       <c r="H45" s="10">
-        <v>200800</v>
+        <v>450000</v>
       </c>
       <c r="I45" s="2">
         <f t="shared" si="13"/>
-        <v>46156</v>
+        <v>46168</v>
       </c>
       <c r="J45" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K45" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -3036,11 +3042,11 @@
       </c>
       <c r="L45" s="1">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M45" s="1">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -3048,46 +3054,46 @@
         <v>67</v>
       </c>
       <c r="B46" s="2">
-        <v>46066</v>
+        <v>46114</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D46" s="1">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E46" s="7">
-        <v>169000</v>
+        <v>80000</v>
       </c>
       <c r="F46" s="13">
         <f t="shared" si="12"/>
-        <v>845000</v>
+        <v>2335000</v>
       </c>
       <c r="G46" s="7">
-        <v>1183000</v>
+        <v>2720000</v>
       </c>
       <c r="H46" s="10">
-        <v>338000</v>
+        <v>385000</v>
       </c>
       <c r="I46" s="2">
         <f t="shared" si="13"/>
-        <v>46156</v>
+        <v>46149</v>
       </c>
       <c r="J46" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="K46" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
-        <v>VIGENTE</v>
+        <v>PRÓXIMO</v>
       </c>
       <c r="L46" s="1">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M46" s="1">
         <f t="shared" si="17"/>
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -3095,28 +3101,30 @@
         <v>68</v>
       </c>
       <c r="B47" s="2">
-        <v>46067</v>
-      </c>
-      <c r="C47" s="1"/>
+        <v>46054</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="D47" s="1">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E47" s="7">
-        <v>25000</v>
+        <v>200000</v>
       </c>
       <c r="F47" s="13">
         <f t="shared" si="12"/>
-        <v>175000</v>
+        <v>1600000</v>
       </c>
       <c r="G47" s="7">
+        <v>2000000</v>
+      </c>
+      <c r="H47" s="10">
         <v>400000</v>
-      </c>
-      <c r="H47" s="10">
-        <v>225000</v>
       </c>
       <c r="I47" s="2">
         <f t="shared" si="13"/>
-        <v>46130</v>
+        <v>46144</v>
       </c>
       <c r="J47" s="1">
         <f t="shared" ca="1" si="14"/>
@@ -3128,11 +3136,11 @@
       </c>
       <c r="L47" s="1">
         <f t="shared" si="16"/>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M47" s="1">
         <f t="shared" si="17"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -3140,34 +3148,34 @@
         <v>69</v>
       </c>
       <c r="B48" s="2">
-        <v>46073</v>
+        <v>46083</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D48" s="1">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E48" s="7">
-        <v>30000</v>
+        <v>80000</v>
       </c>
       <c r="F48" s="13">
         <f t="shared" si="12"/>
-        <v>600000</v>
+        <v>240000</v>
       </c>
       <c r="G48" s="7">
-        <v>750000</v>
+        <v>320000</v>
       </c>
       <c r="H48" s="10">
-        <v>150000</v>
+        <v>80000</v>
       </c>
       <c r="I48" s="2">
         <f t="shared" si="13"/>
-        <v>46115</v>
+        <v>46143</v>
       </c>
       <c r="J48" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>-19</v>
+        <v>-5</v>
       </c>
       <c r="K48" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -3175,11 +3183,11 @@
       </c>
       <c r="L48" s="1">
         <f t="shared" si="16"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M48" s="1">
         <f t="shared" si="17"/>
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -3187,46 +3195,46 @@
         <v>70</v>
       </c>
       <c r="B49" s="2">
-        <v>46078</v>
+        <v>46024</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="D49" s="1">
         <v>30</v>
       </c>
       <c r="E49" s="7">
-        <v>150000</v>
+        <v>170000</v>
       </c>
       <c r="F49" s="13">
         <f t="shared" si="12"/>
-        <v>1200000</v>
+        <v>850000</v>
       </c>
       <c r="G49" s="7">
-        <v>1500000</v>
+        <v>1360000</v>
       </c>
       <c r="H49" s="10">
-        <v>300000</v>
+        <v>510000</v>
       </c>
       <c r="I49" s="2">
         <f t="shared" si="13"/>
-        <v>46138</v>
+        <v>46144</v>
       </c>
       <c r="J49" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="K49" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
-        <v>VIGENTE</v>
+        <v>VENCIDO</v>
       </c>
       <c r="L49" s="1">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M49" s="1">
         <f t="shared" si="17"/>
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -3234,46 +3242,46 @@
         <v>71</v>
       </c>
       <c r="B50" s="2">
-        <v>46114</v>
+        <v>46087</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D50" s="1">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E50" s="7">
-        <v>80000</v>
+        <v>1350000</v>
       </c>
       <c r="F50" s="13">
         <f t="shared" si="12"/>
-        <v>2495000</v>
+        <v>1081721</v>
       </c>
       <c r="G50" s="7">
-        <v>2720000</v>
+        <v>1350000</v>
       </c>
       <c r="H50" s="10">
-        <v>225000</v>
+        <v>268279</v>
       </c>
       <c r="I50" s="2">
         <f t="shared" si="13"/>
-        <v>46135</v>
+        <v>46117</v>
       </c>
       <c r="J50" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>1</v>
+        <v>-31</v>
       </c>
       <c r="K50" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
-        <v>PRÓXIMO</v>
+        <v>VENCIDO</v>
       </c>
       <c r="L50" s="1">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M50" s="1">
         <f t="shared" si="17"/>
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -3281,7 +3289,7 @@
         <v>72</v>
       </c>
       <c r="B51" s="2">
-        <v>46054</v>
+        <v>46087</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>14</v>
@@ -3290,115 +3298,113 @@
         <v>30</v>
       </c>
       <c r="E51" s="7">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F51" s="13">
         <f t="shared" si="12"/>
-        <v>1600000</v>
+        <v>900000</v>
       </c>
       <c r="G51" s="7">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="H51" s="10">
-        <v>400000</v>
+        <v>100000</v>
       </c>
       <c r="I51" s="2">
         <f t="shared" si="13"/>
-        <v>46144</v>
+        <v>46147</v>
       </c>
       <c r="J51" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="K51" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
-        <v>VIGENTE</v>
+        <v>VENCIDO</v>
       </c>
       <c r="L51" s="1">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M51" s="1">
         <f t="shared" si="17"/>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B52" s="2">
-        <v>46083</v>
+        <v>46095</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D52" s="1">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E52" s="7">
-        <v>80000</v>
+        <v>76000</v>
       </c>
       <c r="F52" s="13">
         <f t="shared" si="12"/>
-        <v>240000</v>
+        <v>380000</v>
       </c>
       <c r="G52" s="7">
-        <v>320000</v>
+        <v>760000</v>
       </c>
       <c r="H52" s="10">
-        <v>80000</v>
+        <v>380000</v>
       </c>
       <c r="I52" s="2">
         <f t="shared" si="13"/>
-        <v>46143</v>
+        <v>46137</v>
       </c>
       <c r="J52" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>9</v>
+        <v>-11</v>
       </c>
       <c r="K52" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
-        <v>VIGENTE</v>
+        <v>VENCIDO</v>
       </c>
       <c r="L52" s="1">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M52" s="1">
         <f t="shared" si="17"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B53" s="2">
-        <v>46104</v>
+        <v>46102</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D53" s="1">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E53" s="7">
-        <v>1027000</v>
+        <v>200000</v>
       </c>
       <c r="F53" s="13">
         <f t="shared" si="12"/>
-        <v>759500</v>
+        <v>800000</v>
       </c>
       <c r="G53" s="7">
-        <v>2259500</v>
-      </c>
-      <c r="H53" s="10">
-        <v>1500000</v>
-      </c>
+        <v>800000</v>
+      </c>
+      <c r="H53" s="10"/>
       <c r="I53" s="2">
         <f t="shared" si="13"/>
-        <v>46118</v>
+        <v>46132</v>
       </c>
       <c r="J53" s="1">
         <f t="shared" ca="1" si="14"/>
@@ -3410,46 +3416,44 @@
       </c>
       <c r="L53" s="1">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" s="1">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B54" s="2">
-        <v>46024</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>46114</v>
+      </c>
+      <c r="C54" s="1"/>
       <c r="D54" s="1">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E54" s="7">
-        <v>170000</v>
+        <v>1000000</v>
       </c>
       <c r="F54" s="13">
         <f t="shared" si="12"/>
-        <v>850000</v>
+        <v>49292200</v>
       </c>
       <c r="G54" s="7">
-        <v>1360000</v>
+        <v>100231200</v>
       </c>
       <c r="H54" s="10">
-        <v>510000</v>
+        <v>50939000</v>
       </c>
       <c r="I54" s="2">
         <f t="shared" si="13"/>
-        <v>46144</v>
+        <v>46164</v>
       </c>
       <c r="J54" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K54" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -3457,46 +3461,46 @@
       </c>
       <c r="L54" s="1">
         <f t="shared" si="16"/>
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="M54" s="1">
         <f t="shared" si="17"/>
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="1" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="B55" s="2">
-        <v>46087</v>
+        <v>46114</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D55" s="1">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E55" s="7">
-        <v>1350000</v>
+        <v>500000</v>
       </c>
       <c r="F55" s="13">
         <f t="shared" si="12"/>
-        <v>1081721</v>
+        <v>3426500</v>
       </c>
       <c r="G55" s="7">
-        <v>1350000</v>
+        <v>3926500</v>
       </c>
       <c r="H55" s="10">
-        <v>268279</v>
+        <v>500000</v>
       </c>
       <c r="I55" s="2">
         <f t="shared" si="13"/>
-        <v>46117</v>
+        <v>46116</v>
       </c>
       <c r="J55" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>-17</v>
+        <v>-32</v>
       </c>
       <c r="K55" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -3504,93 +3508,87 @@
       </c>
       <c r="L55" s="1">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="1">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="1" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="B56" s="2">
-        <v>46087</v>
+        <v>46116</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D56" s="1">
-        <v>30</v>
-      </c>
+      <c r="D56" s="1"/>
       <c r="E56" s="7">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="F56" s="13">
         <f t="shared" si="12"/>
-        <v>900000</v>
+        <v>2292000</v>
       </c>
       <c r="G56" s="7">
-        <v>1000000</v>
+        <v>2592000</v>
       </c>
       <c r="H56" s="10">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="I56" s="2">
         <f t="shared" si="13"/>
-        <v>46147</v>
+        <v>46116</v>
       </c>
       <c r="J56" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>13</v>
+        <v>-32</v>
       </c>
       <c r="K56" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
-        <v>VIGENTE</v>
+        <v>VENCIDO</v>
       </c>
       <c r="L56" s="1">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>300000</v>
       </c>
       <c r="M56" s="1">
         <f t="shared" si="17"/>
-        <v>9</v>
+        <v>2292000</v>
       </c>
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B57" s="2">
-        <v>46095</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D57" s="1">
-        <v>7</v>
-      </c>
+        <v>46119</v>
+      </c>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
       <c r="E57" s="7">
-        <v>76000</v>
+        <v>59000</v>
       </c>
       <c r="F57" s="13">
         <f t="shared" si="12"/>
-        <v>456000</v>
+        <v>59000</v>
       </c>
       <c r="G57" s="7">
-        <v>760000</v>
+        <v>236000</v>
       </c>
       <c r="H57" s="10">
-        <v>304000</v>
+        <v>177000</v>
       </c>
       <c r="I57" s="2">
         <f t="shared" si="13"/>
-        <v>46130</v>
+        <v>46119</v>
       </c>
       <c r="J57" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>-4</v>
+        <v>-29</v>
       </c>
       <c r="K57" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -3598,19 +3596,19 @@
       </c>
       <c r="L57" s="1">
         <f t="shared" si="16"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M57" s="1">
         <f t="shared" si="17"/>
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B58" s="2">
-        <v>46102</v>
+        <v>46120</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>14</v>
@@ -3619,27 +3617,27 @@
         <v>30</v>
       </c>
       <c r="E58" s="7">
-        <v>200000</v>
+        <v>99500</v>
       </c>
       <c r="F58" s="13">
         <f t="shared" si="12"/>
-        <v>800000</v>
+        <v>597000</v>
       </c>
       <c r="G58" s="7">
-        <v>800000</v>
+        <v>597000</v>
       </c>
       <c r="H58" s="10"/>
       <c r="I58" s="2">
         <f t="shared" si="13"/>
-        <v>46132</v>
+        <v>46150</v>
       </c>
       <c r="J58" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="K58" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
-        <v>VENCIDO</v>
+        <v>VIGENTE</v>
       </c>
       <c r="L58" s="1">
         <f t="shared" si="16"/>
@@ -3647,175 +3645,177 @@
       </c>
       <c r="M58" s="1">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B59" s="2">
-        <v>46114</v>
+        <v>46127</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1">
         <v>1</v>
       </c>
       <c r="E59" s="7">
-        <v>1000000</v>
+        <v>12500</v>
       </c>
       <c r="F59" s="13">
         <f t="shared" si="12"/>
-        <v>45592200</v>
+        <v>75000</v>
       </c>
       <c r="G59" s="7">
-        <v>95031200</v>
+        <v>125000</v>
       </c>
       <c r="H59" s="10">
-        <v>49439000</v>
+        <v>50000</v>
       </c>
       <c r="I59" s="2">
         <f t="shared" si="13"/>
-        <v>46163</v>
+        <v>46131</v>
       </c>
       <c r="J59" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>29</v>
+        <v>-17</v>
       </c>
       <c r="K59" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
-        <v>VIGENTE</v>
+        <v>VENCIDO</v>
       </c>
       <c r="L59" s="1">
         <f t="shared" si="16"/>
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="M59" s="1">
         <f t="shared" si="17"/>
-        <v>46</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B60" s="2">
-        <v>46114</v>
+        <v>46129</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D60" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E60" s="7">
-        <v>500000</v>
+        <v>25000</v>
       </c>
       <c r="F60" s="13">
         <f t="shared" si="12"/>
-        <v>3426500</v>
+        <v>250000</v>
       </c>
       <c r="G60" s="7">
-        <v>3926500</v>
+        <v>325000</v>
       </c>
       <c r="H60" s="10">
-        <v>500000</v>
+        <v>75000</v>
       </c>
       <c r="I60" s="2">
         <f t="shared" si="13"/>
-        <v>46116</v>
+        <v>46157</v>
       </c>
       <c r="J60" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>-18</v>
+        <v>9</v>
       </c>
       <c r="K60" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
-        <v>VENCIDO</v>
+        <v>VIGENTE</v>
       </c>
       <c r="L60" s="1">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M60" s="1">
         <f t="shared" si="17"/>
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="1" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="B61" s="2">
-        <v>46116</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D61" s="1"/>
+        <v>46130</v>
+      </c>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1">
+        <v>7</v>
+      </c>
       <c r="E61" s="7">
-        <v>1</v>
+        <v>320000</v>
       </c>
       <c r="F61" s="13">
         <f t="shared" si="12"/>
-        <v>2392000</v>
+        <v>2240000</v>
       </c>
       <c r="G61" s="7">
-        <v>2592000</v>
+        <v>3200000</v>
       </c>
       <c r="H61" s="10">
-        <v>200000</v>
+        <v>960000</v>
       </c>
       <c r="I61" s="2">
         <f t="shared" si="13"/>
-        <v>46116</v>
+        <v>46151</v>
       </c>
       <c r="J61" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>-18</v>
+        <v>3</v>
       </c>
       <c r="K61" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
-        <v>VENCIDO</v>
+        <v>VIGENTE</v>
       </c>
       <c r="L61" s="1">
         <f t="shared" si="16"/>
-        <v>200000</v>
+        <v>3</v>
       </c>
       <c r="M61" s="1">
         <f t="shared" si="17"/>
-        <v>2392000</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B62" s="2">
-        <v>46119</v>
-      </c>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
+        <v>46134</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D62" s="1">
+        <v>7</v>
+      </c>
       <c r="E62" s="7">
-        <v>59000</v>
+        <v>25000</v>
       </c>
       <c r="F62" s="13">
         <f t="shared" si="12"/>
-        <v>118000</v>
+        <v>25000</v>
       </c>
       <c r="G62" s="7">
-        <v>236000</v>
-      </c>
-      <c r="H62" s="10">
-        <v>118000</v>
-      </c>
+        <v>25000</v>
+      </c>
+      <c r="H62" s="10"/>
       <c r="I62" s="2">
         <f t="shared" si="13"/>
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="J62" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>-15</v>
+        <v>-7</v>
       </c>
       <c r="K62" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -3823,48 +3823,48 @@
       </c>
       <c r="L62" s="1">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M62" s="1">
         <f t="shared" si="17"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B63" s="2">
-        <v>46120</v>
+        <v>46134</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D63" s="1">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E63" s="7">
-        <v>99500</v>
+        <v>10</v>
       </c>
       <c r="F63" s="13">
         <f t="shared" si="12"/>
-        <v>597000</v>
+        <v>508000</v>
       </c>
       <c r="G63" s="7">
-        <v>597000</v>
+        <v>508000</v>
       </c>
       <c r="H63" s="10"/>
       <c r="I63" s="2">
         <f t="shared" si="13"/>
-        <v>46150</v>
+        <v>46141</v>
       </c>
       <c r="J63" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>16</v>
+        <v>-7</v>
       </c>
       <c r="K63" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
-        <v>VIGENTE</v>
+        <v>VENCIDO</v>
       </c>
       <c r="L63" s="1">
         <f t="shared" si="16"/>
@@ -3872,46 +3872,44 @@
       </c>
       <c r="M63" s="1">
         <f t="shared" si="17"/>
-        <v>6</v>
+        <v>50800</v>
       </c>
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B64" s="2">
-        <v>46127</v>
+        <v>46135</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D64" s="1">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E64" s="7">
-        <v>287300</v>
+        <v>31000</v>
       </c>
       <c r="F64" s="13">
         <f t="shared" si="12"/>
-        <v>202300</v>
+        <v>580000</v>
       </c>
       <c r="G64" s="7">
-        <v>287300</v>
-      </c>
-      <c r="H64" s="10">
-        <v>85000</v>
-      </c>
+        <v>580000</v>
+      </c>
+      <c r="H64" s="10"/>
       <c r="I64" s="2">
         <f t="shared" si="13"/>
-        <v>46157</v>
+        <v>46142</v>
       </c>
       <c r="J64" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>23</v>
+        <v>-6</v>
       </c>
       <c r="K64" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
-        <v>VIGENTE</v>
+        <v>VENCIDO</v>
       </c>
       <c r="L64" s="1">
         <f t="shared" si="16"/>
@@ -3919,87 +3917,87 @@
       </c>
       <c r="M64" s="1">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B65" s="2">
-        <v>46127</v>
-      </c>
-      <c r="C65" s="1"/>
+        <v>46135</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="D65" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E65" s="7">
-        <v>12500</v>
+        <v>127000</v>
       </c>
       <c r="F65" s="13">
         <f t="shared" si="12"/>
-        <v>75000</v>
+        <v>381000</v>
       </c>
       <c r="G65" s="7">
-        <v>125000</v>
-      </c>
-      <c r="H65" s="10">
-        <v>50000</v>
-      </c>
+        <v>381000</v>
+      </c>
+      <c r="H65" s="10"/>
       <c r="I65" s="2">
         <f t="shared" si="13"/>
-        <v>46131</v>
+        <v>46165</v>
       </c>
       <c r="J65" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>-3</v>
+        <v>17</v>
       </c>
       <c r="K65" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
-        <v>VENCIDO</v>
+        <v>VIGENTE</v>
       </c>
       <c r="L65" s="1">
         <f t="shared" si="16"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M65" s="1">
         <f t="shared" si="17"/>
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B66" s="2">
-        <v>46129</v>
+        <v>46136</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D66" s="1">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E66" s="7">
-        <v>25000</v>
+        <v>90000</v>
       </c>
       <c r="F66" s="13">
         <f t="shared" si="12"/>
-        <v>275000</v>
+        <v>360000</v>
       </c>
       <c r="G66" s="7">
-        <v>325000</v>
+        <v>450000</v>
       </c>
       <c r="H66" s="10">
-        <v>50000</v>
+        <v>90000</v>
       </c>
       <c r="I66" s="2">
         <f t="shared" si="13"/>
-        <v>46150</v>
+        <v>46196</v>
       </c>
       <c r="J66" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="K66" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -4007,46 +4005,44 @@
       </c>
       <c r="L66" s="1">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M66" s="1">
         <f t="shared" si="17"/>
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B67" s="2">
-        <v>46130</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>46136</v>
+      </c>
+      <c r="C67" s="1"/>
       <c r="D67" s="1">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E67" s="7">
-        <v>19000</v>
+        <v>140000</v>
       </c>
       <c r="F67" s="13">
         <f t="shared" si="12"/>
-        <v>19000</v>
+        <v>490000</v>
       </c>
       <c r="G67" s="7">
-        <v>39000</v>
+        <v>630000</v>
       </c>
       <c r="H67" s="10">
-        <v>20000</v>
+        <v>140000</v>
       </c>
       <c r="I67" s="2">
         <f t="shared" si="13"/>
-        <v>46144</v>
+        <v>46166</v>
       </c>
       <c r="J67" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K67" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -4058,40 +4054,42 @@
       </c>
       <c r="M67" s="1">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B68" s="2">
-        <v>46130</v>
-      </c>
-      <c r="C68" s="1"/>
+        <v>46138</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="D68" s="1">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E68" s="7">
-        <v>320000</v>
+        <v>100000</v>
       </c>
       <c r="F68" s="13">
         <f t="shared" si="12"/>
-        <v>2880000</v>
+        <v>300000</v>
       </c>
       <c r="G68" s="7">
-        <v>3200000</v>
+        <v>400000</v>
       </c>
       <c r="H68" s="10">
-        <v>320000</v>
+        <v>100000</v>
       </c>
       <c r="I68" s="2">
         <f t="shared" si="13"/>
-        <v>46137</v>
+        <v>46198</v>
       </c>
       <c r="J68" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="K68" s="3" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -4103,15 +4101,15 @@
       </c>
       <c r="M68" s="1">
         <f t="shared" si="17"/>
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B69" s="2">
-        <v>46134</v>
+        <v>46139</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>14</v>
@@ -4120,380 +4118,420 @@
         <v>7</v>
       </c>
       <c r="E69" s="7">
-        <v>23900</v>
+        <v>250000</v>
       </c>
       <c r="F69" s="13">
-        <f t="shared" si="12"/>
-        <v>23900</v>
+        <f t="shared" ref="F69:F130" si="18">G69-H69</f>
+        <v>250000</v>
       </c>
       <c r="G69" s="7">
-        <v>33900</v>
-      </c>
-      <c r="H69" s="10">
-        <v>10000</v>
-      </c>
+        <v>250000</v>
+      </c>
+      <c r="H69" s="10"/>
       <c r="I69" s="2">
-        <f t="shared" si="13"/>
-        <v>46141</v>
+        <f t="shared" ref="I69:I130" si="19">IF(F69=0,"",IF(C69="CRED",B69+(INT((G69-F69)/E69)+1)*D69,B69+INT((G69-F69)/E69)*D69))</f>
+        <v>46146</v>
       </c>
       <c r="J69" s="1">
-        <f t="shared" ca="1" si="14"/>
-        <v>7</v>
+        <f t="shared" ref="J69:J130" ca="1" si="20">IF(I69="","",I69-TODAY())</f>
+        <v>-2</v>
       </c>
       <c r="K69" s="3" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v>VIGENTE</v>
+        <f t="shared" ref="K69:K130" ca="1" si="21">IF(J69="","",IF(J69&lt;0,"VENCIDO",IF(J69&lt;=1,"PRÓXIMO","VIGENTE")))</f>
+        <v>VENCIDO</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="L69:L130" si="22">IF(F69=G69,0,INT((G69-F69)/E69))</f>
         <v>0</v>
       </c>
       <c r="M69" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="M69:M130" si="23">IF(F69=0,0,INT(F69/E69)+(IF(MOD(F69,E69)&gt;0,1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B70" s="2">
-        <v>46134</v>
+        <v>46141</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D70" s="1">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E70" s="7">
-        <v>10</v>
+        <v>119000</v>
       </c>
       <c r="F70" s="13">
-        <f t="shared" si="12"/>
-        <v>508000</v>
+        <f t="shared" si="18"/>
+        <v>599000</v>
       </c>
       <c r="G70" s="7">
-        <v>508000</v>
-      </c>
-      <c r="H70" s="10"/>
+        <v>718000</v>
+      </c>
+      <c r="H70" s="10">
+        <v>119000</v>
+      </c>
       <c r="I70" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
+        <v>46201</v>
+      </c>
+      <c r="J70" s="1">
+        <f t="shared" ca="1" si="20"/>
+        <v>53</v>
+      </c>
+      <c r="K70" s="3" t="str">
+        <f t="shared" ca="1" si="21"/>
+        <v>VIGENTE</v>
+      </c>
+      <c r="L70" s="1">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+      <c r="M70" s="1">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13">
+      <c r="A71" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B71" s="2">
         <v>46141</v>
       </c>
-      <c r="J70" s="1">
-        <f t="shared" ca="1" si="14"/>
-        <v>7</v>
-      </c>
-      <c r="K70" s="3" t="str">
-        <f t="shared" ca="1" si="15"/>
+      <c r="C71" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D71" s="1">
+        <v>30</v>
+      </c>
+      <c r="E71" s="7">
+        <v>360000</v>
+      </c>
+      <c r="F71" s="13">
+        <f t="shared" si="18"/>
+        <v>360000</v>
+      </c>
+      <c r="G71" s="7">
+        <v>720000</v>
+      </c>
+      <c r="H71" s="10">
+        <v>360000</v>
+      </c>
+      <c r="I71" s="2">
+        <f t="shared" si="19"/>
+        <v>46171</v>
+      </c>
+      <c r="J71" s="1">
+        <f t="shared" ca="1" si="20"/>
+        <v>23</v>
+      </c>
+      <c r="K71" s="3" t="str">
+        <f t="shared" ca="1" si="21"/>
         <v>VIGENTE</v>
       </c>
-      <c r="L70" s="1">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M70" s="1">
-        <f t="shared" si="17"/>
-        <v>50800</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13">
-      <c r="A71" s="1"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="13">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="G71" s="7"/>
-      <c r="H71" s="10"/>
-      <c r="I71" s="2" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="J71" s="1" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-      <c r="K71" s="3" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
       <c r="L71" s="1">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f t="shared" si="22"/>
+        <v>1</v>
       </c>
       <c r="M71" s="1">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:13">
-      <c r="A72" s="1"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="7"/>
+      <c r="A72" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B72" s="2">
+        <v>46141</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D72" s="1">
+        <v>30</v>
+      </c>
+      <c r="E72" s="7">
+        <v>50000</v>
+      </c>
       <c r="F72" s="13">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="G72" s="7"/>
+        <f t="shared" si="18"/>
+        <v>50000</v>
+      </c>
+      <c r="G72" s="7">
+        <v>50000</v>
+      </c>
       <c r="H72" s="10"/>
-      <c r="I72" s="2" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="J72" s="1" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
+      <c r="I72" s="2">
+        <f t="shared" si="19"/>
+        <v>46171</v>
+      </c>
+      <c r="J72" s="1">
+        <f t="shared" ca="1" si="20"/>
+        <v>23</v>
       </c>
       <c r="K72" s="3" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
+        <f t="shared" ca="1" si="21"/>
+        <v>VIGENTE</v>
       </c>
       <c r="L72" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M72" s="1">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:13">
-      <c r="A73" s="1"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="7"/>
+      <c r="A73" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B73" s="2">
+        <v>46144</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D73" s="1">
+        <v>30</v>
+      </c>
+      <c r="E73" s="7">
+        <v>200000</v>
+      </c>
       <c r="F73" s="13">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="G73" s="7"/>
+        <f t="shared" si="18"/>
+        <v>1200000</v>
+      </c>
+      <c r="G73" s="7">
+        <v>1200000</v>
+      </c>
       <c r="H73" s="10"/>
-      <c r="I73" s="2" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="J73" s="1" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
+      <c r="I73" s="2">
+        <f t="shared" si="19"/>
+        <v>46174</v>
+      </c>
+      <c r="J73" s="1">
+        <f t="shared" ca="1" si="20"/>
+        <v>26</v>
       </c>
       <c r="K73" s="3" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
+        <f t="shared" ca="1" si="21"/>
+        <v>VIGENTE</v>
       </c>
       <c r="L73" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M73" s="1">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="23"/>
+        <v>6</v>
       </c>
     </row>
     <row r="74" spans="1:13">
-      <c r="A74" s="1"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="7"/>
+      <c r="A74" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B74" s="2">
+        <v>46144</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D74" s="1">
+        <v>15</v>
+      </c>
+      <c r="E74" s="7">
+        <v>2080000</v>
+      </c>
       <c r="F74" s="13">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="G74" s="7"/>
+        <f t="shared" si="18"/>
+        <v>2080000</v>
+      </c>
+      <c r="G74" s="7">
+        <v>2080000</v>
+      </c>
       <c r="H74" s="10"/>
-      <c r="I74" s="2" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="J74" s="1" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
+      <c r="I74" s="2">
+        <f t="shared" si="19"/>
+        <v>46159</v>
+      </c>
+      <c r="J74" s="1">
+        <f t="shared" ca="1" si="20"/>
+        <v>11</v>
       </c>
       <c r="K74" s="3" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
+        <f t="shared" ca="1" si="21"/>
+        <v>VIGENTE</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M74" s="1">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:13">
-      <c r="A75" s="1"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
-      <c r="E75" s="7"/>
+      <c r="A75" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B75" s="2">
+        <v>46147</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" s="1">
+        <v>15</v>
+      </c>
+      <c r="E75" s="7">
+        <v>52500</v>
+      </c>
       <c r="F75" s="13">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="G75" s="7"/>
+        <f t="shared" si="18"/>
+        <v>52500</v>
+      </c>
+      <c r="G75" s="7">
+        <v>52500</v>
+      </c>
       <c r="H75" s="10"/>
-      <c r="I75" s="2" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="J75" s="1" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
+      <c r="I75" s="2">
+        <f t="shared" si="19"/>
+        <v>46162</v>
+      </c>
+      <c r="J75" s="1">
+        <f t="shared" ca="1" si="20"/>
+        <v>14</v>
       </c>
       <c r="K75" s="3" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
+        <f t="shared" ca="1" si="21"/>
+        <v>VIGENTE</v>
       </c>
       <c r="L75" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M75" s="1">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:13">
       <c r="A76" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B76" s="2">
-        <v>46134</v>
-      </c>
-      <c r="C76" s="1"/>
+        <v>46148</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="D76" s="1">
         <v>7</v>
       </c>
       <c r="E76" s="7">
-        <v>20000</v>
+        <v>22000</v>
       </c>
       <c r="F76" s="13">
-        <f t="shared" si="12"/>
-        <v>180000</v>
+        <f t="shared" si="18"/>
+        <v>176000</v>
       </c>
       <c r="G76" s="7">
-        <v>200000</v>
-      </c>
-      <c r="H76" s="10">
-        <v>20000</v>
-      </c>
+        <v>176000</v>
+      </c>
+      <c r="H76" s="10"/>
       <c r="I76" s="2">
-        <f t="shared" si="13"/>
-        <v>46141</v>
+        <f t="shared" si="19"/>
+        <v>46155</v>
       </c>
       <c r="J76" s="1">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="20"/>
         <v>7</v>
       </c>
       <c r="K76" s="3" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="21"/>
         <v>VIGENTE</v>
       </c>
       <c r="L76" s="1">
-        <f t="shared" si="16"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="M76" s="1">
-        <f t="shared" si="17"/>
-        <v>9</v>
+        <f t="shared" si="23"/>
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:13">
-      <c r="A77" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B77" s="2">
-        <v>46134</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D77" s="1">
-        <v>15</v>
-      </c>
-      <c r="E77" s="7">
-        <v>20000</v>
-      </c>
+      <c r="A77" s="1"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="7"/>
       <c r="F77" s="13">
-        <f t="shared" si="12"/>
-        <v>200000</v>
-      </c>
-      <c r="G77" s="7">
-        <v>200000</v>
-      </c>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="G77" s="7"/>
       <c r="H77" s="10"/>
-      <c r="I77" s="2">
-        <f t="shared" si="13"/>
-        <v>46149</v>
-      </c>
-      <c r="J77" s="1">
-        <f t="shared" ca="1" si="14"/>
-        <v>15</v>
+      <c r="I77" s="2" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="J77" s="1" t="str">
+        <f t="shared" ca="1" si="20"/>
+        <v/>
       </c>
       <c r="K77" s="3" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v>VIGENTE</v>
+        <f t="shared" ca="1" si="21"/>
+        <v/>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M77" s="1">
-        <f t="shared" si="17"/>
-        <v>10</v>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:13">
       <c r="A78" s="1"/>
-      <c r="B78" s="2">
-        <v>46134</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D78" s="1">
-        <v>30</v>
-      </c>
-      <c r="E78" s="7">
-        <v>20000</v>
-      </c>
+      <c r="B78" s="2"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="7"/>
       <c r="F78" s="13">
-        <f t="shared" si="12"/>
-        <v>200000</v>
-      </c>
-      <c r="G78" s="7">
-        <v>200000</v>
-      </c>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="G78" s="7"/>
       <c r="H78" s="10"/>
-      <c r="I78" s="2">
-        <f t="shared" si="13"/>
-        <v>46164</v>
-      </c>
-      <c r="J78" s="1">
-        <f t="shared" ca="1" si="14"/>
-        <v>30</v>
+      <c r="I78" s="2" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="J78" s="1" t="str">
+        <f t="shared" ca="1" si="20"/>
+        <v/>
       </c>
       <c r="K78" s="3" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v>VIGENTE</v>
+        <f t="shared" ca="1" si="21"/>
+        <v/>
       </c>
       <c r="L78" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M78" s="1">
-        <f t="shared" si="17"/>
-        <v>10</v>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -4503,29 +4541,29 @@
       <c r="D79" s="1"/>
       <c r="E79" s="7"/>
       <c r="F79" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="10"/>
       <c r="I79" s="2" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="J79" s="1" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="K79" s="3" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="L79" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M79" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -4536,29 +4574,29 @@
       <c r="D80" s="1"/>
       <c r="E80" s="7"/>
       <c r="F80" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="10"/>
       <c r="I80" s="2" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="J80" s="1" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="K80" s="3" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M80" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -4569,29 +4607,29 @@
       <c r="D81" s="1"/>
       <c r="E81" s="7"/>
       <c r="F81" s="13">
-        <f t="shared" ref="F81:F144" si="18">G81-H81</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="10"/>
       <c r="I81" s="2" t="str">
-        <f t="shared" ref="I81:I144" si="19">IF(F81=0,"",IF(C81="CRED",B81+(INT((G81-F81)/E81)+1)*D81,B81+INT((G81-F81)/E81)*D81))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="J81" s="1" t="str">
-        <f t="shared" ref="J81:J144" ca="1" si="20">IF(I81="","",I81-TODAY())</f>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="K81" s="3" t="str">
-        <f t="shared" ref="K81:K144" ca="1" si="21">IF(J81="","",IF(J81&lt;0,"VENCIDO",IF(J81&lt;=1,"PRÓXIMO","VIGENTE")))</f>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="L81" s="1">
-        <f t="shared" ref="L81:L144" si="22">IF(F81=G81,0,INT((G81-F81)/E81))</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M81" s="1">
-        <f t="shared" ref="M81:M144" si="23">IF(F81=0,0,INT(F81/E81)+(IF(MOD(F81,E81)&gt;0,1,0)))</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -6219,29 +6257,29 @@
       <c r="D131" s="1"/>
       <c r="E131" s="7"/>
       <c r="F131" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="F131:F164" si="24">G131-H131</f>
         <v>0</v>
       </c>
       <c r="G131" s="7"/>
       <c r="H131" s="10"/>
       <c r="I131" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="I131:I164" si="25">IF(F131=0,"",IF(C131="CRED",B131+(INT((G131-F131)/E131)+1)*D131,B131+INT((G131-F131)/E131)*D131))</f>
         <v/>
       </c>
       <c r="J131" s="1" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ref="J131:J164" ca="1" si="26">IF(I131="","",I131-TODAY())</f>
         <v/>
       </c>
       <c r="K131" s="3" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ref="K131:K163" ca="1" si="27">IF(J131="","",IF(J131&lt;0,"VENCIDO",IF(J131&lt;=1,"PRÓXIMO","VIGENTE")))</f>
         <v/>
       </c>
       <c r="L131" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="L131:L164" si="28">IF(F131=G131,0,INT((G131-F131)/E131))</f>
         <v>0</v>
       </c>
       <c r="M131" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="M131:M164" si="29">IF(F131=0,0,INT(F131/E131)+(IF(MOD(F131,E131)&gt;0,1,0)))</f>
         <v>0</v>
       </c>
     </row>
@@ -6252,29 +6290,29 @@
       <c r="D132" s="1"/>
       <c r="E132" s="7"/>
       <c r="F132" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G132" s="7"/>
       <c r="H132" s="10"/>
       <c r="I132" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="J132" s="1" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
       <c r="K132" s="3" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="27"/>
         <v/>
       </c>
       <c r="L132" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M132" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
     </row>
@@ -6285,29 +6323,29 @@
       <c r="D133" s="1"/>
       <c r="E133" s="7"/>
       <c r="F133" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G133" s="7"/>
       <c r="H133" s="10"/>
       <c r="I133" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="J133" s="1" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
       <c r="K133" s="3" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="27"/>
         <v/>
       </c>
       <c r="L133" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M133" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
     </row>
@@ -6318,29 +6356,29 @@
       <c r="D134" s="1"/>
       <c r="E134" s="7"/>
       <c r="F134" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G134" s="7"/>
       <c r="H134" s="10"/>
       <c r="I134" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="J134" s="1" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
       <c r="K134" s="3" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="27"/>
         <v/>
       </c>
       <c r="L134" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M134" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
     </row>
@@ -6351,29 +6389,29 @@
       <c r="D135" s="1"/>
       <c r="E135" s="7"/>
       <c r="F135" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G135" s="7"/>
       <c r="H135" s="10"/>
       <c r="I135" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="J135" s="1" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
       <c r="K135" s="3" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="27"/>
         <v/>
       </c>
       <c r="L135" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M135" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
     </row>
@@ -6384,29 +6422,29 @@
       <c r="D136" s="1"/>
       <c r="E136" s="7"/>
       <c r="F136" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G136" s="7"/>
       <c r="H136" s="10"/>
       <c r="I136" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="J136" s="1" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
       <c r="K136" s="3" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="27"/>
         <v/>
       </c>
       <c r="L136" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M136" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
     </row>
@@ -6417,29 +6455,29 @@
       <c r="D137" s="1"/>
       <c r="E137" s="7"/>
       <c r="F137" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G137" s="7"/>
       <c r="H137" s="10"/>
       <c r="I137" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="J137" s="1" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
       <c r="K137" s="3" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="27"/>
         <v/>
       </c>
       <c r="L137" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M137" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
     </row>
@@ -6450,29 +6488,29 @@
       <c r="D138" s="1"/>
       <c r="E138" s="7"/>
       <c r="F138" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G138" s="7"/>
       <c r="H138" s="10"/>
       <c r="I138" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="J138" s="1" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
       <c r="K138" s="3" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="27"/>
         <v/>
       </c>
       <c r="L138" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M138" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
     </row>
@@ -6483,29 +6521,29 @@
       <c r="D139" s="1"/>
       <c r="E139" s="7"/>
       <c r="F139" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G139" s="7"/>
       <c r="H139" s="10"/>
       <c r="I139" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="J139" s="1" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
       <c r="K139" s="3" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="27"/>
         <v/>
       </c>
       <c r="L139" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M139" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
     </row>
@@ -6516,29 +6554,29 @@
       <c r="D140" s="1"/>
       <c r="E140" s="7"/>
       <c r="F140" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G140" s="7"/>
       <c r="H140" s="10"/>
       <c r="I140" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="J140" s="1" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
       <c r="K140" s="3" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="27"/>
         <v/>
       </c>
       <c r="L140" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M140" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
     </row>
@@ -6549,29 +6587,29 @@
       <c r="D141" s="1"/>
       <c r="E141" s="7"/>
       <c r="F141" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G141" s="7"/>
       <c r="H141" s="10"/>
       <c r="I141" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="J141" s="1" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
       <c r="K141" s="3" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="27"/>
         <v/>
       </c>
       <c r="L141" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M141" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
     </row>
@@ -6582,29 +6620,29 @@
       <c r="D142" s="1"/>
       <c r="E142" s="7"/>
       <c r="F142" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G142" s="7"/>
       <c r="H142" s="10"/>
       <c r="I142" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="J142" s="1" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
       <c r="K142" s="3" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="27"/>
         <v/>
       </c>
       <c r="L142" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M142" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
     </row>
@@ -6615,29 +6653,29 @@
       <c r="D143" s="1"/>
       <c r="E143" s="7"/>
       <c r="F143" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G143" s="7"/>
       <c r="H143" s="10"/>
       <c r="I143" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="J143" s="1" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
       <c r="K143" s="3" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="27"/>
         <v/>
       </c>
       <c r="L143" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M143" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
     </row>
@@ -6648,29 +6686,29 @@
       <c r="D144" s="1"/>
       <c r="E144" s="7"/>
       <c r="F144" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G144" s="7"/>
       <c r="H144" s="10"/>
       <c r="I144" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="J144" s="1" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
       <c r="K144" s="3" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="27"/>
         <v/>
       </c>
       <c r="L144" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M144" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
     </row>
@@ -6681,29 +6719,29 @@
       <c r="D145" s="1"/>
       <c r="E145" s="7"/>
       <c r="F145" s="13">
-        <f t="shared" ref="F145:F178" si="24">G145-H145</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G145" s="7"/>
       <c r="H145" s="10"/>
       <c r="I145" s="2" t="str">
-        <f t="shared" ref="I145:I178" si="25">IF(F145=0,"",IF(C145="CRED",B145+(INT((G145-F145)/E145)+1)*D145,B145+INT((G145-F145)/E145)*D145))</f>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="J145" s="1" t="str">
-        <f t="shared" ref="J145:J178" ca="1" si="26">IF(I145="","",I145-TODAY())</f>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
       <c r="K145" s="3" t="str">
-        <f t="shared" ref="K145:K177" ca="1" si="27">IF(J145="","",IF(J145&lt;0,"VENCIDO",IF(J145&lt;=1,"PRÓXIMO","VIGENTE")))</f>
+        <f t="shared" ca="1" si="27"/>
         <v/>
       </c>
       <c r="L145" s="1">
-        <f t="shared" ref="L145:L178" si="28">IF(F145=G145,0,INT((G145-F145)/E145))</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M145" s="1">
-        <f t="shared" ref="M145:M178" si="29">IF(F145=0,0,INT(F145/E145)+(IF(MOD(F145,E145)&gt;0,1,0)))</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
     </row>
@@ -7322,7 +7360,7 @@
         <v/>
       </c>
       <c r="K164" s="3" t="str">
-        <f t="shared" ca="1" si="27"/>
+        <f ca="1">IF(J164="","",IF(J164&lt;0,"VENCIDO",IF(J164&lt;=1,"PRÓXIMO","VIGENTE")))</f>
         <v/>
       </c>
       <c r="L164" s="1">
@@ -7341,29 +7379,29 @@
       <c r="D165" s="1"/>
       <c r="E165" s="7"/>
       <c r="F165" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="F165:F223" si="30">G165-H165</f>
         <v>0</v>
       </c>
       <c r="G165" s="7"/>
       <c r="H165" s="10"/>
       <c r="I165" s="2" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="I165:I223" si="31">IF(F165=0,"",IF(C165="CRED",B165+(INT((G165-F165)/E165)+1)*D165,B165+INT((G165-F165)/E165)*D165))</f>
         <v/>
       </c>
       <c r="J165" s="1" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ref="J165:J223" ca="1" si="32">IF(I165="","",I165-TODAY())</f>
         <v/>
       </c>
       <c r="K165" s="3" t="str">
-        <f t="shared" ca="1" si="27"/>
+        <f t="shared" ref="K165:K223" ca="1" si="33">IF(J165="","",IF(J165&lt;0,"VENCIDO",IF(J165&lt;=1,"PRÓXIMO","VIGENTE")))</f>
         <v/>
       </c>
       <c r="L165" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="L165:L223" si="34">IF(F165=G165,0,INT((G165-F165)/E165))</f>
         <v>0</v>
       </c>
       <c r="M165" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="M165:M223" si="35">IF(F165=0,0,INT(F165/E165)+(IF(MOD(F165,E165)&gt;0,1,0)))</f>
         <v>0</v>
       </c>
     </row>
@@ -7374,29 +7412,29 @@
       <c r="D166" s="1"/>
       <c r="E166" s="7"/>
       <c r="F166" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G166" s="7"/>
       <c r="H166" s="10"/>
       <c r="I166" s="2" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J166" s="1" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="K166" s="3" t="str">
-        <f t="shared" ca="1" si="27"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="L166" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M166" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
@@ -7407,29 +7445,29 @@
       <c r="D167" s="1"/>
       <c r="E167" s="7"/>
       <c r="F167" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G167" s="7"/>
       <c r="H167" s="10"/>
       <c r="I167" s="2" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J167" s="1" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="K167" s="3" t="str">
-        <f t="shared" ca="1" si="27"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="L167" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M167" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
@@ -7440,29 +7478,29 @@
       <c r="D168" s="1"/>
       <c r="E168" s="7"/>
       <c r="F168" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G168" s="7"/>
       <c r="H168" s="10"/>
       <c r="I168" s="2" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J168" s="1" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="K168" s="3" t="str">
-        <f t="shared" ca="1" si="27"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="L168" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M168" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
@@ -7473,29 +7511,29 @@
       <c r="D169" s="1"/>
       <c r="E169" s="7"/>
       <c r="F169" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G169" s="7"/>
       <c r="H169" s="10"/>
       <c r="I169" s="2" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J169" s="1" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="K169" s="3" t="str">
-        <f t="shared" ca="1" si="27"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="L169" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M169" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
@@ -7506,29 +7544,29 @@
       <c r="D170" s="1"/>
       <c r="E170" s="7"/>
       <c r="F170" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G170" s="7"/>
       <c r="H170" s="10"/>
       <c r="I170" s="2" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J170" s="1" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="K170" s="3" t="str">
-        <f t="shared" ca="1" si="27"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="L170" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M170" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
@@ -7539,29 +7577,29 @@
       <c r="D171" s="1"/>
       <c r="E171" s="7"/>
       <c r="F171" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G171" s="7"/>
       <c r="H171" s="10"/>
       <c r="I171" s="2" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J171" s="1" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="K171" s="3" t="str">
-        <f t="shared" ca="1" si="27"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="L171" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M171" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
@@ -7572,29 +7610,29 @@
       <c r="D172" s="1"/>
       <c r="E172" s="7"/>
       <c r="F172" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G172" s="7"/>
       <c r="H172" s="10"/>
       <c r="I172" s="2" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J172" s="1" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="K172" s="3" t="str">
-        <f t="shared" ca="1" si="27"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="L172" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M172" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
@@ -7605,29 +7643,29 @@
       <c r="D173" s="1"/>
       <c r="E173" s="7"/>
       <c r="F173" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G173" s="7"/>
       <c r="H173" s="10"/>
       <c r="I173" s="2" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J173" s="1" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="K173" s="3" t="str">
-        <f t="shared" ca="1" si="27"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="L173" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M173" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
@@ -7638,29 +7676,29 @@
       <c r="D174" s="1"/>
       <c r="E174" s="7"/>
       <c r="F174" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G174" s="7"/>
       <c r="H174" s="10"/>
       <c r="I174" s="2" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J174" s="1" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="K174" s="3" t="str">
-        <f t="shared" ca="1" si="27"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="L174" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M174" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
@@ -7671,29 +7709,29 @@
       <c r="D175" s="1"/>
       <c r="E175" s="7"/>
       <c r="F175" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G175" s="7"/>
       <c r="H175" s="10"/>
       <c r="I175" s="2" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J175" s="1" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="K175" s="3" t="str">
-        <f t="shared" ca="1" si="27"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="L175" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M175" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
@@ -7704,29 +7742,29 @@
       <c r="D176" s="1"/>
       <c r="E176" s="7"/>
       <c r="F176" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G176" s="7"/>
       <c r="H176" s="10"/>
       <c r="I176" s="2" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J176" s="1" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="K176" s="3" t="str">
-        <f t="shared" ca="1" si="27"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="L176" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M176" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
@@ -7737,29 +7775,29 @@
       <c r="D177" s="1"/>
       <c r="E177" s="7"/>
       <c r="F177" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G177" s="7"/>
       <c r="H177" s="10"/>
       <c r="I177" s="2" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J177" s="1" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="K177" s="3" t="str">
-        <f t="shared" ca="1" si="27"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="L177" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M177" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
@@ -7770,29 +7808,29 @@
       <c r="D178" s="1"/>
       <c r="E178" s="7"/>
       <c r="F178" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G178" s="7"/>
       <c r="H178" s="10"/>
       <c r="I178" s="2" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J178" s="1" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="K178" s="3" t="str">
-        <f ca="1">IF(J178="","",IF(J178&lt;0,"VENCIDO",IF(J178&lt;=1,"PRÓXIMO","VIGENTE")))</f>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="L178" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M178" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
@@ -7803,29 +7841,29 @@
       <c r="D179" s="1"/>
       <c r="E179" s="7"/>
       <c r="F179" s="13">
-        <f t="shared" ref="F179:F237" si="30">G179-H179</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G179" s="7"/>
       <c r="H179" s="10"/>
       <c r="I179" s="2" t="str">
-        <f t="shared" ref="I179:I237" si="31">IF(F179=0,"",IF(C179="CRED",B179+(INT((G179-F179)/E179)+1)*D179,B179+INT((G179-F179)/E179)*D179))</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J179" s="1" t="str">
-        <f t="shared" ref="J179:J237" ca="1" si="32">IF(I179="","",I179-TODAY())</f>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="K179" s="3" t="str">
-        <f t="shared" ref="K179:K237" ca="1" si="33">IF(J179="","",IF(J179&lt;0,"VENCIDO",IF(J179&lt;=1,"PRÓXIMO","VIGENTE")))</f>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="L179" s="1">
-        <f t="shared" ref="L179:L237" si="34">IF(F179=G179,0,INT((G179-F179)/E179))</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M179" s="1">
-        <f t="shared" ref="M179:M237" si="35">IF(F179=0,0,INT(F179/E179)+(IF(MOD(F179,E179)&gt;0,1,0)))</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
@@ -9281,480 +9319,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:13">
-      <c r="A224" s="1"/>
-      <c r="B224" s="2"/>
-      <c r="C224" s="1"/>
-      <c r="D224" s="1"/>
-      <c r="E224" s="7"/>
-      <c r="F224" s="13">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G224" s="7"/>
-      <c r="H224" s="10"/>
-      <c r="I224" s="2" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="J224" s="1" t="str">
-        <f t="shared" ca="1" si="32"/>
-        <v/>
-      </c>
-      <c r="K224" s="3" t="str">
-        <f t="shared" ca="1" si="33"/>
-        <v/>
-      </c>
-      <c r="L224" s="1">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="M224" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225" spans="1:13">
-      <c r="A225" s="1"/>
-      <c r="B225" s="2"/>
-      <c r="C225" s="1"/>
-      <c r="D225" s="1"/>
-      <c r="E225" s="7"/>
-      <c r="F225" s="13">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G225" s="7"/>
-      <c r="H225" s="10"/>
-      <c r="I225" s="2" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="J225" s="1" t="str">
-        <f t="shared" ca="1" si="32"/>
-        <v/>
-      </c>
-      <c r="K225" s="3" t="str">
-        <f t="shared" ca="1" si="33"/>
-        <v/>
-      </c>
-      <c r="L225" s="1">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="M225" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" spans="1:13">
-      <c r="A226" s="1"/>
-      <c r="B226" s="2"/>
-      <c r="C226" s="1"/>
-      <c r="D226" s="1"/>
-      <c r="E226" s="7"/>
-      <c r="F226" s="13">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G226" s="7"/>
-      <c r="H226" s="10"/>
-      <c r="I226" s="2" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="J226" s="1" t="str">
-        <f t="shared" ca="1" si="32"/>
-        <v/>
-      </c>
-      <c r="K226" s="3" t="str">
-        <f t="shared" ca="1" si="33"/>
-        <v/>
-      </c>
-      <c r="L226" s="1">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="M226" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" spans="1:13">
-      <c r="A227" s="1"/>
-      <c r="B227" s="2"/>
-      <c r="C227" s="1"/>
-      <c r="D227" s="1"/>
-      <c r="E227" s="7"/>
-      <c r="F227" s="13">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G227" s="7"/>
-      <c r="H227" s="10"/>
-      <c r="I227" s="2" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="J227" s="1" t="str">
-        <f t="shared" ca="1" si="32"/>
-        <v/>
-      </c>
-      <c r="K227" s="3" t="str">
-        <f t="shared" ca="1" si="33"/>
-        <v/>
-      </c>
-      <c r="L227" s="1">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="M227" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228" spans="1:13">
-      <c r="A228" s="1"/>
-      <c r="B228" s="2"/>
-      <c r="C228" s="1"/>
-      <c r="D228" s="1"/>
-      <c r="E228" s="7"/>
-      <c r="F228" s="13">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G228" s="7"/>
-      <c r="H228" s="10"/>
-      <c r="I228" s="2" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="J228" s="1" t="str">
-        <f t="shared" ca="1" si="32"/>
-        <v/>
-      </c>
-      <c r="K228" s="3" t="str">
-        <f t="shared" ca="1" si="33"/>
-        <v/>
-      </c>
-      <c r="L228" s="1">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="M228" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229" spans="1:13">
-      <c r="A229" s="1"/>
-      <c r="B229" s="2"/>
-      <c r="C229" s="1"/>
-      <c r="D229" s="1"/>
-      <c r="E229" s="7"/>
-      <c r="F229" s="13">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G229" s="7"/>
-      <c r="H229" s="10"/>
-      <c r="I229" s="2" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="J229" s="1" t="str">
-        <f t="shared" ca="1" si="32"/>
-        <v/>
-      </c>
-      <c r="K229" s="3" t="str">
-        <f t="shared" ca="1" si="33"/>
-        <v/>
-      </c>
-      <c r="L229" s="1">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="M229" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="230" spans="1:13">
-      <c r="A230" s="1"/>
-      <c r="B230" s="2"/>
-      <c r="C230" s="1"/>
-      <c r="D230" s="1"/>
-      <c r="E230" s="7"/>
-      <c r="F230" s="13">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G230" s="7"/>
-      <c r="H230" s="10"/>
-      <c r="I230" s="2" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="J230" s="1" t="str">
-        <f t="shared" ca="1" si="32"/>
-        <v/>
-      </c>
-      <c r="K230" s="3" t="str">
-        <f t="shared" ca="1" si="33"/>
-        <v/>
-      </c>
-      <c r="L230" s="1">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="M230" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231" spans="1:13">
-      <c r="A231" s="1"/>
-      <c r="B231" s="2"/>
-      <c r="C231" s="1"/>
-      <c r="D231" s="1"/>
-      <c r="E231" s="7"/>
-      <c r="F231" s="13">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G231" s="7"/>
-      <c r="H231" s="10"/>
-      <c r="I231" s="2" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="J231" s="1" t="str">
-        <f t="shared" ca="1" si="32"/>
-        <v/>
-      </c>
-      <c r="K231" s="3" t="str">
-        <f t="shared" ca="1" si="33"/>
-        <v/>
-      </c>
-      <c r="L231" s="1">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="M231" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232" spans="1:13">
-      <c r="A232" s="1"/>
-      <c r="B232" s="2"/>
-      <c r="C232" s="1"/>
-      <c r="D232" s="1"/>
-      <c r="E232" s="7"/>
-      <c r="F232" s="13">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G232" s="7"/>
-      <c r="H232" s="10"/>
-      <c r="I232" s="2" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="J232" s="1" t="str">
-        <f t="shared" ca="1" si="32"/>
-        <v/>
-      </c>
-      <c r="K232" s="3" t="str">
-        <f t="shared" ca="1" si="33"/>
-        <v/>
-      </c>
-      <c r="L232" s="1">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="M232" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233" spans="1:13">
-      <c r="A233" s="1"/>
-      <c r="B233" s="2"/>
-      <c r="C233" s="1"/>
-      <c r="D233" s="1"/>
-      <c r="E233" s="7"/>
-      <c r="F233" s="13">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G233" s="7"/>
-      <c r="H233" s="10"/>
-      <c r="I233" s="2" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="J233" s="1" t="str">
-        <f t="shared" ca="1" si="32"/>
-        <v/>
-      </c>
-      <c r="K233" s="3" t="str">
-        <f t="shared" ca="1" si="33"/>
-        <v/>
-      </c>
-      <c r="L233" s="1">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="M233" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" spans="1:13">
-      <c r="A234" s="1"/>
-      <c r="B234" s="2"/>
-      <c r="C234" s="1"/>
-      <c r="D234" s="1"/>
-      <c r="E234" s="7"/>
-      <c r="F234" s="13">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G234" s="7"/>
-      <c r="H234" s="10"/>
-      <c r="I234" s="2" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="J234" s="1" t="str">
-        <f t="shared" ca="1" si="32"/>
-        <v/>
-      </c>
-      <c r="K234" s="3" t="str">
-        <f t="shared" ca="1" si="33"/>
-        <v/>
-      </c>
-      <c r="L234" s="1">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="M234" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235" spans="1:13">
-      <c r="A235" s="1"/>
-      <c r="B235" s="2"/>
-      <c r="C235" s="1"/>
-      <c r="D235" s="1"/>
-      <c r="E235" s="7"/>
-      <c r="F235" s="13">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G235" s="7"/>
-      <c r="H235" s="10"/>
-      <c r="I235" s="2" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="J235" s="1" t="str">
-        <f t="shared" ca="1" si="32"/>
-        <v/>
-      </c>
-      <c r="K235" s="3" t="str">
-        <f t="shared" ca="1" si="33"/>
-        <v/>
-      </c>
-      <c r="L235" s="1">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="M235" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="236" spans="1:13">
-      <c r="A236" s="1"/>
-      <c r="B236" s="2"/>
-      <c r="C236" s="1"/>
-      <c r="D236" s="1"/>
-      <c r="E236" s="7"/>
-      <c r="F236" s="13">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G236" s="7"/>
-      <c r="H236" s="10"/>
-      <c r="I236" s="2" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="J236" s="1" t="str">
-        <f t="shared" ca="1" si="32"/>
-        <v/>
-      </c>
-      <c r="K236" s="3" t="str">
-        <f t="shared" ca="1" si="33"/>
-        <v/>
-      </c>
-      <c r="L236" s="1">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="M236" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="237" spans="1:13">
-      <c r="A237" s="1"/>
-      <c r="B237" s="2"/>
-      <c r="C237" s="1"/>
-      <c r="D237" s="1"/>
-      <c r="E237" s="7"/>
-      <c r="F237" s="13">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G237" s="7"/>
-      <c r="H237" s="10"/>
-      <c r="I237" s="2" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="J237" s="1" t="str">
-        <f t="shared" ca="1" si="32"/>
-        <v/>
-      </c>
-      <c r="K237" s="3" t="str">
-        <f t="shared" ca="1" si="33"/>
-        <v/>
-      </c>
-      <c r="L237" s="1">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="M237" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="K2:K237">
+  <conditionalFormatting sqref="K2:K223">
     <cfRule type="expression" dxfId="11" priority="6">
       <formula>$K2="VENCIDO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K237">
+  <conditionalFormatting sqref="K2:K223">
     <cfRule type="expression" dxfId="10" priority="5">
       <formula>$K2="PRÓXIMO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K237">
+  <conditionalFormatting sqref="K2:K223">
     <cfRule type="expression" dxfId="9" priority="4">
       <formula>$K2="VIGENTE"</formula>
     </cfRule>
@@ -9787,7 +9363,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
@@ -10030,7 +9606,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="16"/>
       <c r="G15" s="7"/>
-      <c r="H15" s="21"/>
+      <c r="H15" s="20"/>
       <c r="I15" s="2"/>
       <c r="J15" s="1"/>
       <c r="K15" s="3"/>
@@ -10233,8 +9809,8 @@
       <c r="M28" s="1"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="24" t="s">
-        <v>33</v>
+      <c r="A29" s="23" t="s">
+        <v>31</v>
       </c>
       <c r="B29" s="2">
         <v>45969</v>
@@ -10264,7 +9840,7 @@
       </c>
       <c r="J29" s="1">
         <f t="shared" ref="J29:J38" ca="1" si="2">IF(I29="","",I29-TODAY())</f>
-        <v>-144</v>
+        <v>-158</v>
       </c>
       <c r="K29" s="3" t="str">
         <f t="shared" ref="K29:K38" ca="1" si="3">IF(J29="","",IF(J29&lt;0,"VENCIDO",IF(J29&lt;=1,"PRÓXIMO","VIGENTE")))</f>
@@ -10281,9 +9857,9 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="23">
+        <v>32</v>
+      </c>
+      <c r="B30" s="22">
         <v>45961</v>
       </c>
       <c r="C30" s="1"/>
@@ -10309,7 +9885,7 @@
       </c>
       <c r="J30" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-145</v>
+        <v>-159</v>
       </c>
       <c r="K30" s="3" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -10326,7 +9902,7 @@
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="18" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B31" s="2">
         <v>45972</v>
@@ -10354,7 +9930,7 @@
       </c>
       <c r="J31" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-141</v>
+        <v>-155</v>
       </c>
       <c r="K31" s="3" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -10370,8 +9946,8 @@
       </c>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="24" t="s">
-        <v>37</v>
+      <c r="A32" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="B32" s="2">
         <v>45976</v>
@@ -10401,7 +9977,7 @@
       </c>
       <c r="J32" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-144</v>
+        <v>-158</v>
       </c>
       <c r="K32" s="3" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -10418,7 +9994,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="18" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B33" s="2">
         <v>45980</v>
@@ -10448,7 +10024,7 @@
       </c>
       <c r="J33" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-124</v>
+        <v>-138</v>
       </c>
       <c r="K33" s="3" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -10464,8 +10040,8 @@
       </c>
     </row>
     <row r="34" spans="1:13">
-      <c r="A34" s="24" t="s">
-        <v>42</v>
+      <c r="A34" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="B34" s="2">
         <v>45983</v>
@@ -10495,7 +10071,7 @@
       </c>
       <c r="J34" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-137</v>
+        <v>-151</v>
       </c>
       <c r="K34" s="3" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -10521,7 +10097,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="7"/>
-      <c r="H35" s="21"/>
+      <c r="H35" s="20"/>
       <c r="I35" s="2" t="str">
         <f t="shared" si="1"/>
         <v/>
